--- a/data/project-dashboard.xlsx
+++ b/data/project-dashboard.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF233BC7-E6BD-4A3D-B665-255D811A054A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project_Info" sheetId="1" r:id="rId1"/>

--- a/data/project-dashboard.xlsx
+++ b/data/project-dashboard.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF233BC7-E6BD-4A3D-B665-255D811A054A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project_Info" sheetId="1" r:id="rId1"/>
@@ -7202,10 +7202,6 @@
   </cellStyles>
   <dxfs count="35">
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF006100"/>
       </font>
@@ -7363,6 +7359,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -9404,7 +9404,7 @@
     <tableColumn id="10" xr3:uid="{9EAC2262-2A27-42A8-BB73-73F39AFC4912}" name="Schedule % Complete" dataDxfId="25" dataCellStyle="Per cent"/>
     <tableColumn id="11" xr3:uid="{B218F782-EF65-4945-9E84-E0A88975643B}" name="Performance % Complete" dataDxfId="24" dataCellStyle="Per cent"/>
     <tableColumn id="12" xr3:uid="{85C93BA9-907D-4549-9ECD-E1601A6B8FF1}" name="Total Float" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{C49B17F2-109E-42EB-814F-75ABCAF72ADF}" name="Critical" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{C49B17F2-109E-42EB-814F-75ABCAF72ADF}" name="Critical" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9426,17 +9426,17 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="IssuesRisksTable" displayName="IssuesRisksTable" ref="A1:I5" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="IssuesRisksTable" displayName="IssuesRisksTable" ref="A1:I5" dataDxfId="21">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Risk ID" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Risk Description" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Impact Summary" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Probability" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Impact" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Risk Level" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Risk Owner" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Mitigation" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="Target Date" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Risk ID" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Risk Description" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Impact Summary" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Probability" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Impact" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Risk Level" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Risk Owner" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Mitigation" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="Target Date" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9458,15 +9458,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{A2B8666E-147E-4183-82CC-79B74FF1D518}" name="SPITrendTable17" displayName="SPITrendTable17" ref="A1:J2">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{60CDD5EE-B607-4D51-A2AC-550AB14A03F3}" name="Month"/>
-    <tableColumn id="2" xr3:uid="{76772940-DA13-40AE-BA52-917177C89224}" name="01-Feb-2026" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{F0248E2B-506D-42FB-B594-3D1B0C0B4368}" name="01-Mar-2026" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{1235EC57-E169-4937-B53F-0C4A6D4C5E0F}" name="01-Apr-2026" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{7E0642A5-711D-421D-9854-5659F4096F36}" name="01-May-2026" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{88D79C57-C3FB-4564-A7BE-EDB347046130}" name="01-Jun-2026" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{FBD55C5C-8427-4396-A9A1-D8D5EEDAA0F8}" name="01-Jul-2026" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{16A53D90-2572-4B4A-B792-FF1B1888C5A4}" name="01-Aug-2026" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{153860B1-419C-48D2-8D33-F85625CFBC01}" name="01-Sep-2026" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{C6E67E4F-856C-4338-B620-93C903A271F9}" name="01-Oct-2026" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{76772940-DA13-40AE-BA52-917177C89224}" name="01-Feb-2026" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{F0248E2B-506D-42FB-B594-3D1B0C0B4368}" name="01-Mar-2026" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{1235EC57-E169-4937-B53F-0C4A6D4C5E0F}" name="01-Apr-2026" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{7E0642A5-711D-421D-9854-5659F4096F36}" name="01-May-2026" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{88D79C57-C3FB-4564-A7BE-EDB347046130}" name="01-Jun-2026" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{FBD55C5C-8427-4396-A9A1-D8D5EEDAA0F8}" name="01-Jul-2026" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{16A53D90-2572-4B4A-B792-FF1B1888C5A4}" name="01-Aug-2026" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{153860B1-419C-48D2-8D33-F85625CFBC01}" name="01-Sep-2026" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{C6E67E4F-856C-4338-B620-93C903A271F9}" name="01-Oct-2026" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10120,7 +10120,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10257,10 +10257,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThanOrEqual">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/project-dashboard.xlsx
+++ b/data/project-dashboard.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD47F9BD-2FA8-4059-B9BB-FD6C86D2B1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project_Info" sheetId="1" r:id="rId1"/>

--- a/data/project-dashboard.xlsx
+++ b/data/project-dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00-Maseel Project Control\11-Website Dashboard\Dynamic Web\project-dashboard-website\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD47F9BD-2FA8-4059-B9BB-FD6C86D2B1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB51AB52-382A-4DC3-A8EF-B22C0B9AF1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project_Info" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,9 @@
     <sheet name="Site_Photos" sheetId="7" r:id="rId7"/>
     <sheet name="SPI Trend" sheetId="8" r:id="rId8"/>
     <sheet name="S-Curve" sheetId="9" r:id="rId9"/>
-    <sheet name="Website_API_Map" sheetId="10" r:id="rId10"/>
-    <sheet name="Website_Setup" sheetId="11" r:id="rId11"/>
+    <sheet name="Lookahead_3Weeks" sheetId="12" r:id="rId10"/>
+    <sheet name="Website_API_Map" sheetId="10" r:id="rId11"/>
+    <sheet name="Website_Setup" sheetId="11" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10031" uniqueCount="2308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10440" uniqueCount="2308">
   <si>
     <t>Project Name</t>
   </si>
@@ -7131,7 +7132,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -7239,9 +7240,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -7251,6 +7249,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -7258,30 +7260,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="43">
+  <dxfs count="46">
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
     </dxf>
     <dxf>
       <font>
@@ -7444,6 +7431,30 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -7474,6 +7485,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
@@ -7482,16 +7503,6 @@
           <color indexed="64"/>
         </right>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9409,6 +9420,25 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{63CF4BD0-58E1-4A31-B532-77FDF440E2C9}" name="Look_Ahead" displayName="Look_Ahead" ref="A1:J75" totalsRowShown="0">
+  <autoFilter ref="A1:J75" xr:uid="{63CF4BD0-58E1-4A31-B532-77FDF440E2C9}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{057A596C-1792-405A-90C5-8318C14D4D97}" name="Activity ID"/>
+    <tableColumn id="2" xr3:uid="{1E3CDF14-2CB8-4DEF-9547-89E06C85CFF9}" name="Activity Name"/>
+    <tableColumn id="3" xr3:uid="{BEBE23B0-DD9A-46A0-83F0-F7AADFB113E0}" name="Original Duration"/>
+    <tableColumn id="4" xr3:uid="{6FF22079-BD1C-473D-8452-4351A338CF7F}" name="Activity Status"/>
+    <tableColumn id="5" xr3:uid="{07E5DDBB-1EE3-4BBE-A76E-96D7AC3BF882}" name="02- Con.Phase"/>
+    <tableColumn id="6" xr3:uid="{551887B7-0CF0-4401-9C1A-2DF3FF831FD4}" name="Start" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{947F443A-6D45-4251-B1BF-9CBC39B7A1B5}" name="Finish" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{62C03662-69E1-4727-A2DD-0879099C639A}" name="Performance % Complete" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{5C1834A0-CE32-4342-8EF5-1EC543B01FAA}" name="Total Float"/>
+    <tableColumn id="10" xr3:uid="{0293C0C3-272F-4BB3-B63E-9D3BC97471CF}" name="Critical"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="WebsiteAPIMapTable" displayName="WebsiteAPIMapTable" ref="A1:E10">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Purpose"/>
@@ -9430,13 +9460,13 @@
     <tableColumn id="4" xr3:uid="{26228A24-7B89-4F53-8C02-895BDE96807E}" name="Variance %">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{043BEE59-9BB9-48CA-BCAF-B0B49AB502E6}" name="SPI" dataDxfId="42">
+    <tableColumn id="5" xr3:uid="{043BEE59-9BB9-48CA-BCAF-B0B49AB502E6}" name="SPI" dataDxfId="43">
       <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{7FA7C1AA-84AA-4AEE-BAFB-D3FAEE25A5D8}" name="BL Start Date"/>
     <tableColumn id="7" xr3:uid="{4234B7FF-F64E-4A3A-9F37-5B5BEF6D9017}" name="BL Finish Date"/>
     <tableColumn id="8" xr3:uid="{3B605CB7-AB94-4F24-892D-8D23051F549D}" name="Forecast Finish Date"/>
-    <tableColumn id="9" xr3:uid="{8627A771-209F-4934-998C-3A0C21C0CC0E}" name="Variance Finish Date" dataDxfId="41">
+    <tableColumn id="9" xr3:uid="{8627A771-209F-4934-998C-3A0C21C0CC0E}" name="Variance Finish Date" dataDxfId="42">
       <calculatedColumnFormula>G2-H2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{E446F1CD-F15A-4A57-924F-E08331EF6928}" name="Project Duration"/>
@@ -9446,7 +9476,7 @@
     <tableColumn id="12" xr3:uid="{C8177739-B2D6-445C-909A-3B630381521D}" name="Remaining Time">
       <calculatedColumnFormula>J2-K2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{2413F253-FC61-4728-AA12-82814EB1AC1E}" name="Time Elapsed %" dataDxfId="40">
+    <tableColumn id="13" xr3:uid="{2413F253-FC61-4728-AA12-82814EB1AC1E}" name="Time Elapsed %" dataDxfId="41">
       <calculatedColumnFormula>K2/J2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9460,10 +9490,10 @@
     <tableColumn id="1" xr3:uid="{5CC08CFD-BB32-42AE-8929-3D92342465CF}" name="Phase"/>
     <tableColumn id="2" xr3:uid="{5D73634F-CCC4-411A-8B1A-98488EA6FA8F}" name="Planned %"/>
     <tableColumn id="3" xr3:uid="{32C402C6-661D-4391-B7B2-C3C85BB5AF80}" name="Actual %"/>
-    <tableColumn id="4" xr3:uid="{089AD09E-CE81-45D7-9664-49ACA4EE345D}" name="Variance" dataDxfId="39">
+    <tableColumn id="4" xr3:uid="{089AD09E-CE81-45D7-9664-49ACA4EE345D}" name="Variance" dataDxfId="45">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FA9B9069-F615-43F7-AF56-68E6B97329D8}" name="SPI" dataDxfId="38">
+    <tableColumn id="5" xr3:uid="{FA9B9069-F615-43F7-AF56-68E6B97329D8}" name="SPI" dataDxfId="44">
       <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9479,46 +9509,46 @@
     <tableColumn id="3" xr3:uid="{EEFE8DE6-C657-48D9-88FA-7D5A43C1590A}" name="Original Duration"/>
     <tableColumn id="4" xr3:uid="{BFD618A5-3D3D-4C62-9AEE-667429FF6625}" name="Activity Status"/>
     <tableColumn id="5" xr3:uid="{54C85E9C-40B3-4A27-A7A1-08D5632ACFD5}" name="02- Con.Phase"/>
-    <tableColumn id="6" xr3:uid="{1E54E21F-3570-4379-98B5-D3F79BAD2A54}" name="BL Project Start" dataDxfId="37"/>
-    <tableColumn id="7" xr3:uid="{8AF72BC8-3D95-4695-BE78-28DE430A0C96}" name="BL Project Finish" dataDxfId="36"/>
-    <tableColumn id="8" xr3:uid="{41D5B848-CED1-4B85-B7C0-0C2EEADFA08F}" name="Start" dataDxfId="35"/>
-    <tableColumn id="9" xr3:uid="{6993DFB5-C059-4A89-9ABD-71F49C2A6F74}" name="Finish" dataDxfId="34"/>
-    <tableColumn id="10" xr3:uid="{9EAC2262-2A27-42A8-BB73-73F39AFC4912}" name="Schedule % Complete" dataDxfId="33" dataCellStyle="Per cent"/>
-    <tableColumn id="11" xr3:uid="{B218F782-EF65-4945-9E84-E0A88975643B}" name="Performance % Complete" dataDxfId="32" dataCellStyle="Per cent"/>
-    <tableColumn id="12" xr3:uid="{85C93BA9-907D-4549-9ECD-E1601A6B8FF1}" name="Total Float" dataDxfId="31"/>
-    <tableColumn id="13" xr3:uid="{C49B17F2-109E-42EB-814F-75ABCAF72ADF}" name="Critical" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{1E54E21F-3570-4379-98B5-D3F79BAD2A54}" name="BL Project Start" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{8AF72BC8-3D95-4695-BE78-28DE430A0C96}" name="BL Project Finish" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{41D5B848-CED1-4B85-B7C0-0C2EEADFA08F}" name="Start" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{6993DFB5-C059-4A89-9ABD-71F49C2A6F74}" name="Finish" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{9EAC2262-2A27-42A8-BB73-73F39AFC4912}" name="Schedule % Complete" dataDxfId="36" dataCellStyle="Per cent"/>
+    <tableColumn id="11" xr3:uid="{B218F782-EF65-4945-9E84-E0A88975643B}" name="Performance % Complete" dataDxfId="35" dataCellStyle="Per cent"/>
+    <tableColumn id="12" xr3:uid="{85C93BA9-907D-4549-9ECD-E1601A6B8FF1}" name="Total Float" dataDxfId="34"/>
+    <tableColumn id="13" xr3:uid="{C49B17F2-109E-42EB-814F-75ABCAF72ADF}" name="Critical" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{646BB870-B00C-435D-A3B9-FC5EE922B49E}" name="DelaysTable16" displayName="DelaysTable16" ref="A1:G7" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{646BB870-B00C-435D-A3B9-FC5EE922B49E}" name="DelaysTable16" displayName="DelaysTable16" ref="A1:G7" dataDxfId="32">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{432610E1-EB61-4ACD-97A4-8A63654F84F9}" name="Phase Delay/Ahead" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{2C5412A7-92CE-4EAC-8330-FA329E02B968}" name="BL Finish Date" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{0E5F2071-69D2-4243-B28B-C06740FB7648}" name="Forecast Finish Date" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{E02C79E2-295D-4560-9843-63A6C0451E21}" name="Variance Finish Date" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{5A1277A0-CB8F-43B1-BC65-D584276375E2}" name="Delay Reason" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{3E4DC573-6186-4CC7-8D6B-0A44D59D4182}" name="Recovery Action" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{C16296EE-BD20-4329-86E5-BA92EF668C0A}" name="Responsible" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{432610E1-EB61-4ACD-97A4-8A63654F84F9}" name="Phase Delay/Ahead" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{2C5412A7-92CE-4EAC-8330-FA329E02B968}" name="BL Finish Date" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{0E5F2071-69D2-4243-B28B-C06740FB7648}" name="Forecast Finish Date" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{E02C79E2-295D-4560-9843-63A6C0451E21}" name="Variance Finish Date" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{5A1277A0-CB8F-43B1-BC65-D584276375E2}" name="Delay Reason" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{3E4DC573-6186-4CC7-8D6B-0A44D59D4182}" name="Recovery Action" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{C16296EE-BD20-4329-86E5-BA92EF668C0A}" name="Responsible" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="IssuesRisksTable" displayName="IssuesRisksTable" ref="A1:I6" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="IssuesRisksTable" displayName="IssuesRisksTable" ref="A1:I6" dataDxfId="24">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Risk ID" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Risk Description" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Impact Summary" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Probability" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Impact" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Risk Level" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Risk Owner" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Mitigation" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="Target Date" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Risk ID" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Risk Description" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Impact Summary" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Probability" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Impact" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Risk Level" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Risk Owner" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Mitigation" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="Target Date" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9540,15 +9570,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{A2B8666E-147E-4183-82CC-79B74FF1D518}" name="SPITrendTable17" displayName="SPITrendTable17" ref="A1:J2">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{60CDD5EE-B607-4D51-A2AC-550AB14A03F3}" name="Month"/>
-    <tableColumn id="2" xr3:uid="{76772940-DA13-40AE-BA52-917177C89224}" name="01-Feb-2026" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{F0248E2B-506D-42FB-B594-3D1B0C0B4368}" name="01-Mar-2026" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{1235EC57-E169-4937-B53F-0C4A6D4C5E0F}" name="01-Apr-2026" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{7E0642A5-711D-421D-9854-5659F4096F36}" name="01-May-2026" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{88D79C57-C3FB-4564-A7BE-EDB347046130}" name="01-Jun-2026" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{FBD55C5C-8427-4396-A9A1-D8D5EEDAA0F8}" name="01-Jul-2026" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{16A53D90-2572-4B4A-B792-FF1B1888C5A4}" name="01-Aug-2026" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{153860B1-419C-48D2-8D33-F85625CFBC01}" name="01-Sep-2026" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{C6E67E4F-856C-4338-B620-93C903A271F9}" name="01-Oct-2026" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{76772940-DA13-40AE-BA52-917177C89224}" name="01-Feb-2026" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{F0248E2B-506D-42FB-B594-3D1B0C0B4368}" name="01-Mar-2026" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{1235EC57-E169-4937-B53F-0C4A6D4C5E0F}" name="01-Apr-2026" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{7E0642A5-711D-421D-9854-5659F4096F36}" name="01-May-2026" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{88D79C57-C3FB-4564-A7BE-EDB347046130}" name="01-Jun-2026" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{FBD55C5C-8427-4396-A9A1-D8D5EEDAA0F8}" name="01-Jul-2026" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{16A53D90-2572-4B4A-B792-FF1B1888C5A4}" name="01-Aug-2026" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{153860B1-419C-48D2-8D33-F85625CFBC01}" name="01-Sep-2026" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{C6E67E4F-856C-4338-B620-93C903A271F9}" name="01-Oct-2026" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9824,6 +9854,2427 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD8E641E-8ADA-437C-9106-D96C97500733}">
+  <dimension ref="A1:J75"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="5" width="14.88671875" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.21875" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2265</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2266</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2267</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2270</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2271</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2273</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2274</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>680</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s">
+        <v>681</v>
+      </c>
+      <c r="F2" t="s">
+        <v>682</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46186</v>
+      </c>
+      <c r="H2" s="43">
+        <v>0.99</v>
+      </c>
+      <c r="I2">
+        <v>-40</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G3" s="1">
+        <v>46187</v>
+      </c>
+      <c r="H3" s="43">
+        <v>0.91</v>
+      </c>
+      <c r="I3">
+        <v>-50</v>
+      </c>
+      <c r="J3" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C4">
+        <v>55</v>
+      </c>
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1699</v>
+      </c>
+      <c r="G4" s="1">
+        <v>46184</v>
+      </c>
+      <c r="H4" s="43">
+        <v>0.99</v>
+      </c>
+      <c r="I4">
+        <v>-22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>166</v>
+      </c>
+      <c r="G5" s="1">
+        <v>46184</v>
+      </c>
+      <c r="H5" s="43">
+        <v>0.95</v>
+      </c>
+      <c r="I5">
+        <v>-43</v>
+      </c>
+      <c r="J5" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1956</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G6" s="1">
+        <v>46184</v>
+      </c>
+      <c r="H6" s="43">
+        <v>0.95</v>
+      </c>
+      <c r="I6">
+        <v>-35</v>
+      </c>
+      <c r="J6" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G7" s="1">
+        <v>46184</v>
+      </c>
+      <c r="H7" s="43">
+        <v>0.95</v>
+      </c>
+      <c r="I7">
+        <v>-43</v>
+      </c>
+      <c r="J7" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="1">
+        <v>46188</v>
+      </c>
+      <c r="H8" s="43">
+        <v>0.9</v>
+      </c>
+      <c r="I8">
+        <v>-43</v>
+      </c>
+      <c r="J8" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G9" t="s">
+        <v>2292</v>
+      </c>
+      <c r="H9" s="43">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1961</v>
+      </c>
+      <c r="G10" s="1">
+        <v>46202</v>
+      </c>
+      <c r="H10" s="43">
+        <v>0.05</v>
+      </c>
+      <c r="I10">
+        <v>-50</v>
+      </c>
+      <c r="J10" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1961</v>
+      </c>
+      <c r="G11" s="1">
+        <v>46188</v>
+      </c>
+      <c r="H11" s="43">
+        <v>0.9</v>
+      </c>
+      <c r="I11">
+        <v>-35</v>
+      </c>
+      <c r="J11" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" t="s">
+        <v>149</v>
+      </c>
+      <c r="G12" s="1">
+        <v>46193</v>
+      </c>
+      <c r="H12" s="43">
+        <v>0.95</v>
+      </c>
+      <c r="I12">
+        <v>-25</v>
+      </c>
+      <c r="J12" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G13" s="1">
+        <v>46193</v>
+      </c>
+      <c r="H13" s="43">
+        <v>0.9</v>
+      </c>
+      <c r="I13">
+        <v>-35</v>
+      </c>
+      <c r="J13" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C14">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1702</v>
+      </c>
+      <c r="G14" s="1">
+        <v>46191</v>
+      </c>
+      <c r="H14" s="43">
+        <v>0.96</v>
+      </c>
+      <c r="I14">
+        <v>-22</v>
+      </c>
+      <c r="J14" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="1">
+        <v>46187</v>
+      </c>
+      <c r="H15" s="43">
+        <v>0.95</v>
+      </c>
+      <c r="I15">
+        <v>-41</v>
+      </c>
+      <c r="J15" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" t="s">
+        <v>151</v>
+      </c>
+      <c r="G16" s="1">
+        <v>46196</v>
+      </c>
+      <c r="H16" s="43">
+        <v>0.6</v>
+      </c>
+      <c r="I16">
+        <v>-25</v>
+      </c>
+      <c r="J16" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F17" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="1">
+        <v>46203</v>
+      </c>
+      <c r="H17" s="43">
+        <v>0.6</v>
+      </c>
+      <c r="I17">
+        <v>-35</v>
+      </c>
+      <c r="J17" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F18" t="s">
+        <v>167</v>
+      </c>
+      <c r="G18" s="1">
+        <v>46189</v>
+      </c>
+      <c r="H18" s="43">
+        <v>0.9</v>
+      </c>
+      <c r="I18">
+        <v>-39</v>
+      </c>
+      <c r="J18" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F19" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="1">
+        <v>46187</v>
+      </c>
+      <c r="H19" s="43">
+        <v>0.9</v>
+      </c>
+      <c r="I19">
+        <v>-15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>171</v>
+      </c>
+      <c r="B20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" t="s">
+        <v>172</v>
+      </c>
+      <c r="G20" s="1">
+        <v>46187</v>
+      </c>
+      <c r="H20" s="43">
+        <v>0.7</v>
+      </c>
+      <c r="I20">
+        <v>-26</v>
+      </c>
+      <c r="J20" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F21" t="s">
+        <v>172</v>
+      </c>
+      <c r="G21" s="1">
+        <v>46195</v>
+      </c>
+      <c r="H21" s="43">
+        <v>0.3</v>
+      </c>
+      <c r="I21">
+        <v>-50</v>
+      </c>
+      <c r="J21" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>688</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" t="s">
+        <v>681</v>
+      </c>
+      <c r="F22" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" s="1">
+        <v>46187</v>
+      </c>
+      <c r="H22" s="43">
+        <v>0.95</v>
+      </c>
+      <c r="I22">
+        <v>-40</v>
+      </c>
+      <c r="J22" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>191</v>
+      </c>
+      <c r="B23" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" t="s">
+        <v>2277</v>
+      </c>
+      <c r="G23" s="1">
+        <v>46194</v>
+      </c>
+      <c r="H23" s="43">
+        <v>0.35</v>
+      </c>
+      <c r="I23">
+        <v>-40</v>
+      </c>
+      <c r="J23" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>689</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" t="s">
+        <v>681</v>
+      </c>
+      <c r="F24" t="s">
+        <v>2277</v>
+      </c>
+      <c r="G24" s="1">
+        <v>46190</v>
+      </c>
+      <c r="H24" s="43">
+        <v>0.7</v>
+      </c>
+      <c r="I24">
+        <v>-40</v>
+      </c>
+      <c r="J24" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B25" t="s">
+        <v>686</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F25" t="s">
+        <v>2276</v>
+      </c>
+      <c r="G25" s="1">
+        <v>46188</v>
+      </c>
+      <c r="H25" s="43">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>-50</v>
+      </c>
+      <c r="J25" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>701</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" t="s">
+        <v>681</v>
+      </c>
+      <c r="F26" t="s">
+        <v>2275</v>
+      </c>
+      <c r="G26" s="1">
+        <v>46196</v>
+      </c>
+      <c r="H26" s="43">
+        <v>0.7</v>
+      </c>
+      <c r="I26">
+        <v>-36</v>
+      </c>
+      <c r="J26" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" t="s">
+        <v>2291</v>
+      </c>
+      <c r="G27" s="1">
+        <v>46194</v>
+      </c>
+      <c r="H27" s="43">
+        <v>0.1</v>
+      </c>
+      <c r="I27">
+        <v>-41</v>
+      </c>
+      <c r="J27" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>195</v>
+      </c>
+      <c r="B28" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28">
+        <v>6</v>
+      </c>
+      <c r="D28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" t="s">
+        <v>2293</v>
+      </c>
+      <c r="G28" s="1">
+        <v>46197</v>
+      </c>
+      <c r="H28" s="43">
+        <v>0.1</v>
+      </c>
+      <c r="I28">
+        <v>-40</v>
+      </c>
+      <c r="J28" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B29" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F29" t="s">
+        <v>2293</v>
+      </c>
+      <c r="G29" s="1">
+        <v>46197</v>
+      </c>
+      <c r="H29" s="43">
+        <v>0.05</v>
+      </c>
+      <c r="I29">
+        <v>-39</v>
+      </c>
+      <c r="J29" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>203</v>
+      </c>
+      <c r="B30" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30">
+        <v>6</v>
+      </c>
+      <c r="D30" t="s">
+        <v>186</v>
+      </c>
+      <c r="E30" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" s="1">
+        <v>46184</v>
+      </c>
+      <c r="G30" s="1">
+        <v>46190</v>
+      </c>
+      <c r="H30" s="43">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>-27</v>
+      </c>
+      <c r="J30" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>204</v>
+      </c>
+      <c r="B31" t="s">
+        <v>194</v>
+      </c>
+      <c r="C31">
+        <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>186</v>
+      </c>
+      <c r="E31" t="s">
+        <v>35</v>
+      </c>
+      <c r="F31" s="1">
+        <v>46184</v>
+      </c>
+      <c r="G31" s="1">
+        <v>46190</v>
+      </c>
+      <c r="H31" s="43">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>-23</v>
+      </c>
+      <c r="J31" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>215</v>
+      </c>
+      <c r="B32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C32">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" t="s">
+        <v>35</v>
+      </c>
+      <c r="F32" s="1">
+        <v>46188</v>
+      </c>
+      <c r="G32" s="1">
+        <v>46194</v>
+      </c>
+      <c r="H32" s="43">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>-26</v>
+      </c>
+      <c r="J32" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B33" t="s">
+        <v>684</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>186</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F33" s="1">
+        <v>46188</v>
+      </c>
+      <c r="G33" s="1">
+        <v>46188</v>
+      </c>
+      <c r="H33" s="43">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>-50</v>
+      </c>
+      <c r="J33" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>216</v>
+      </c>
+      <c r="B34" t="s">
+        <v>194</v>
+      </c>
+      <c r="C34">
+        <v>6</v>
+      </c>
+      <c r="D34" t="s">
+        <v>186</v>
+      </c>
+      <c r="E34" t="s">
+        <v>35</v>
+      </c>
+      <c r="F34" s="1">
+        <v>46188</v>
+      </c>
+      <c r="G34" s="1">
+        <v>46194</v>
+      </c>
+      <c r="H34" s="43">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>-24</v>
+      </c>
+      <c r="J34" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35">
+        <v>9</v>
+      </c>
+      <c r="D35" t="s">
+        <v>186</v>
+      </c>
+      <c r="E35" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" s="1">
+        <v>46188</v>
+      </c>
+      <c r="G35" s="1">
+        <v>46198</v>
+      </c>
+      <c r="H35" s="43">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>-43</v>
+      </c>
+      <c r="J35" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C36">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F36" s="1">
+        <v>46189</v>
+      </c>
+      <c r="G36" s="1">
+        <v>46202</v>
+      </c>
+      <c r="H36" s="43">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>-22</v>
+      </c>
+      <c r="J36" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>217</v>
+      </c>
+      <c r="B37" t="s">
+        <v>196</v>
+      </c>
+      <c r="C37">
+        <v>6</v>
+      </c>
+      <c r="D37" t="s">
+        <v>186</v>
+      </c>
+      <c r="E37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="1">
+        <v>46190</v>
+      </c>
+      <c r="G37" s="1">
+        <v>46196</v>
+      </c>
+      <c r="H37" s="43">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>-26</v>
+      </c>
+      <c r="J37" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>690</v>
+      </c>
+      <c r="B38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
+        <v>186</v>
+      </c>
+      <c r="E38" t="s">
+        <v>681</v>
+      </c>
+      <c r="F38" s="1">
+        <v>46191</v>
+      </c>
+      <c r="G38" s="1">
+        <v>46195</v>
+      </c>
+      <c r="H38" s="43">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>-41</v>
+      </c>
+      <c r="J38" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>197</v>
+      </c>
+      <c r="B39" t="s">
+        <v>198</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+      <c r="D39" t="s">
+        <v>186</v>
+      </c>
+      <c r="E39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" s="1">
+        <v>46193</v>
+      </c>
+      <c r="G39" s="1">
+        <v>46198</v>
+      </c>
+      <c r="H39" s="43">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>-41</v>
+      </c>
+      <c r="J39" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>218</v>
+      </c>
+      <c r="B40" t="s">
+        <v>219</v>
+      </c>
+      <c r="C40">
+        <v>6</v>
+      </c>
+      <c r="D40" t="s">
+        <v>186</v>
+      </c>
+      <c r="E40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F40" s="1">
+        <v>46193</v>
+      </c>
+      <c r="G40" s="1">
+        <v>46198</v>
+      </c>
+      <c r="H40" s="43">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>-24</v>
+      </c>
+      <c r="J40" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B41" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41">
+        <v>10</v>
+      </c>
+      <c r="D41" t="s">
+        <v>186</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F41" s="1">
+        <v>46193</v>
+      </c>
+      <c r="G41" s="1">
+        <v>46203</v>
+      </c>
+      <c r="H41" s="43">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>8</v>
+      </c>
+      <c r="J41" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B42" t="s">
+        <v>198</v>
+      </c>
+      <c r="C42">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s">
+        <v>186</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F42" s="1">
+        <v>46195</v>
+      </c>
+      <c r="G42" s="1">
+        <v>46202</v>
+      </c>
+      <c r="H42" s="43">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>-39</v>
+      </c>
+      <c r="J42" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43" t="s">
+        <v>186</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F43" s="1">
+        <v>46196</v>
+      </c>
+      <c r="G43" s="1">
+        <v>46198</v>
+      </c>
+      <c r="H43" s="43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>-50</v>
+      </c>
+      <c r="J43" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>691</v>
+      </c>
+      <c r="B44" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44" t="s">
+        <v>186</v>
+      </c>
+      <c r="E44" t="s">
+        <v>681</v>
+      </c>
+      <c r="F44" s="1">
+        <v>46196</v>
+      </c>
+      <c r="G44" s="1">
+        <v>46198</v>
+      </c>
+      <c r="H44" s="43">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>-41</v>
+      </c>
+      <c r="J44" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>702</v>
+      </c>
+      <c r="B45" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45" t="s">
+        <v>186</v>
+      </c>
+      <c r="E45" t="s">
+        <v>681</v>
+      </c>
+      <c r="F45" s="1">
+        <v>46196</v>
+      </c>
+      <c r="G45" s="1">
+        <v>46200</v>
+      </c>
+      <c r="H45" s="43">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>-36</v>
+      </c>
+      <c r="J45" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>713</v>
+      </c>
+      <c r="B46" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46">
+        <v>5</v>
+      </c>
+      <c r="D46" t="s">
+        <v>186</v>
+      </c>
+      <c r="E46" t="s">
+        <v>681</v>
+      </c>
+      <c r="F46" s="1">
+        <v>46196</v>
+      </c>
+      <c r="G46" s="1">
+        <v>46202</v>
+      </c>
+      <c r="H46" s="43">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>-36</v>
+      </c>
+      <c r="J46" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>209</v>
+      </c>
+      <c r="B47" t="s">
+        <v>192</v>
+      </c>
+      <c r="C47">
+        <v>6</v>
+      </c>
+      <c r="D47" t="s">
+        <v>186</v>
+      </c>
+      <c r="E47" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" s="1">
+        <v>46197</v>
+      </c>
+      <c r="G47" s="1">
+        <v>46203</v>
+      </c>
+      <c r="H47" s="43">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>-25</v>
+      </c>
+      <c r="J47" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>220</v>
+      </c>
+      <c r="B48" t="s">
+        <v>200</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>186</v>
+      </c>
+      <c r="E48" t="s">
+        <v>35</v>
+      </c>
+      <c r="F48" s="1">
+        <v>46197</v>
+      </c>
+      <c r="G48" s="1">
+        <v>46197</v>
+      </c>
+      <c r="H48" s="43">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>-26</v>
+      </c>
+      <c r="J48" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>210</v>
+      </c>
+      <c r="B49" t="s">
+        <v>194</v>
+      </c>
+      <c r="C49">
+        <v>6</v>
+      </c>
+      <c r="D49" t="s">
+        <v>186</v>
+      </c>
+      <c r="E49" t="s">
+        <v>35</v>
+      </c>
+      <c r="F49" s="1">
+        <v>46197</v>
+      </c>
+      <c r="G49" s="1">
+        <v>46203</v>
+      </c>
+      <c r="H49" s="43">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>-22</v>
+      </c>
+      <c r="J49" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" t="s">
+        <v>200</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50" t="s">
+        <v>186</v>
+      </c>
+      <c r="E50" t="s">
+        <v>35</v>
+      </c>
+      <c r="F50" s="1">
+        <v>46198</v>
+      </c>
+      <c r="G50" s="1">
+        <v>46198</v>
+      </c>
+      <c r="H50" s="43">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>-40</v>
+      </c>
+      <c r="J50" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>187</v>
+      </c>
+      <c r="B51" t="s">
+        <v>84</v>
+      </c>
+      <c r="C51">
+        <v>6</v>
+      </c>
+      <c r="D51" t="s">
+        <v>186</v>
+      </c>
+      <c r="E51" t="s">
+        <v>35</v>
+      </c>
+      <c r="F51" s="1">
+        <v>46198</v>
+      </c>
+      <c r="G51" s="1">
+        <v>46205</v>
+      </c>
+      <c r="H51" s="43">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>-43</v>
+      </c>
+      <c r="J51" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>201</v>
+      </c>
+      <c r="B52" t="s">
+        <v>202</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52" t="s">
+        <v>186</v>
+      </c>
+      <c r="E52" t="s">
+        <v>35</v>
+      </c>
+      <c r="F52" s="1">
+        <v>46200</v>
+      </c>
+      <c r="G52" s="1">
+        <v>46202</v>
+      </c>
+      <c r="H52" s="43">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>-41</v>
+      </c>
+      <c r="J52" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>221</v>
+      </c>
+      <c r="B53" t="s">
+        <v>202</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53" t="s">
+        <v>186</v>
+      </c>
+      <c r="E53" t="s">
+        <v>35</v>
+      </c>
+      <c r="F53" s="1">
+        <v>46200</v>
+      </c>
+      <c r="G53" s="1">
+        <v>46202</v>
+      </c>
+      <c r="H53" s="43">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>-24</v>
+      </c>
+      <c r="J53" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B54" t="s">
+        <v>202</v>
+      </c>
+      <c r="C54">
+        <v>7</v>
+      </c>
+      <c r="D54" t="s">
+        <v>186</v>
+      </c>
+      <c r="E54" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F54" s="1">
+        <v>46200</v>
+      </c>
+      <c r="G54" s="1">
+        <v>46207</v>
+      </c>
+      <c r="H54" s="43">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>-39</v>
+      </c>
+      <c r="J54" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>693</v>
+      </c>
+      <c r="B55" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>186</v>
+      </c>
+      <c r="E55" t="s">
+        <v>681</v>
+      </c>
+      <c r="F55" s="1">
+        <v>46200</v>
+      </c>
+      <c r="G55" s="1">
+        <v>46201</v>
+      </c>
+      <c r="H55" s="43">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>-41</v>
+      </c>
+      <c r="J55" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>703</v>
+      </c>
+      <c r="B56" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56">
+        <v>3</v>
+      </c>
+      <c r="D56" t="s">
+        <v>186</v>
+      </c>
+      <c r="E56" t="s">
+        <v>681</v>
+      </c>
+      <c r="F56" s="1">
+        <v>46200</v>
+      </c>
+      <c r="G56" s="1">
+        <v>46203</v>
+      </c>
+      <c r="H56" s="43">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>-36</v>
+      </c>
+      <c r="J56" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>211</v>
+      </c>
+      <c r="B57" t="s">
+        <v>196</v>
+      </c>
+      <c r="C57">
+        <v>6</v>
+      </c>
+      <c r="D57" t="s">
+        <v>186</v>
+      </c>
+      <c r="E57" t="s">
+        <v>35</v>
+      </c>
+      <c r="F57" s="1">
+        <v>46201</v>
+      </c>
+      <c r="G57" s="1">
+        <v>46207</v>
+      </c>
+      <c r="H57" s="43">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>-25</v>
+      </c>
+      <c r="J57" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B58" t="s">
+        <v>192</v>
+      </c>
+      <c r="C58">
+        <v>7</v>
+      </c>
+      <c r="D58" t="s">
+        <v>186</v>
+      </c>
+      <c r="E58" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F58" s="1">
+        <v>46202</v>
+      </c>
+      <c r="G58" s="1">
+        <v>46209</v>
+      </c>
+      <c r="H58" s="43">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>-38</v>
+      </c>
+      <c r="J58" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B59" t="s">
+        <v>192</v>
+      </c>
+      <c r="C59">
+        <v>7</v>
+      </c>
+      <c r="D59" t="s">
+        <v>186</v>
+      </c>
+      <c r="E59" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F59" s="1">
+        <v>46202</v>
+      </c>
+      <c r="G59" s="1">
+        <v>46209</v>
+      </c>
+      <c r="H59" s="43">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>-27</v>
+      </c>
+      <c r="J59" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>212</v>
+      </c>
+      <c r="B60" t="s">
+        <v>198</v>
+      </c>
+      <c r="C60">
+        <v>6</v>
+      </c>
+      <c r="D60" t="s">
+        <v>186</v>
+      </c>
+      <c r="E60" t="s">
+        <v>35</v>
+      </c>
+      <c r="F60" s="1">
+        <v>46202</v>
+      </c>
+      <c r="G60" s="1">
+        <v>46208</v>
+      </c>
+      <c r="H60" s="43">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>-22</v>
+      </c>
+      <c r="J60" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B61" t="s">
+        <v>194</v>
+      </c>
+      <c r="C61">
+        <v>7</v>
+      </c>
+      <c r="D61" t="s">
+        <v>186</v>
+      </c>
+      <c r="E61" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F61" s="1">
+        <v>46202</v>
+      </c>
+      <c r="G61" s="1">
+        <v>46209</v>
+      </c>
+      <c r="H61" s="43">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>-38</v>
+      </c>
+      <c r="J61" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B62" t="s">
+        <v>194</v>
+      </c>
+      <c r="C62">
+        <v>7</v>
+      </c>
+      <c r="D62" t="s">
+        <v>186</v>
+      </c>
+      <c r="E62" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F62" s="1">
+        <v>46202</v>
+      </c>
+      <c r="G62" s="1">
+        <v>46209</v>
+      </c>
+      <c r="H62" s="43">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>-27</v>
+      </c>
+      <c r="J62" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>694</v>
+      </c>
+      <c r="B63" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63">
+        <v>4</v>
+      </c>
+      <c r="D63" t="s">
+        <v>186</v>
+      </c>
+      <c r="E63" t="s">
+        <v>681</v>
+      </c>
+      <c r="F63" s="1">
+        <v>46202</v>
+      </c>
+      <c r="G63" s="1">
+        <v>46205</v>
+      </c>
+      <c r="H63" s="43">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>-41</v>
+      </c>
+      <c r="J63" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>188</v>
+      </c>
+      <c r="B64" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64">
+        <v>7</v>
+      </c>
+      <c r="D64" t="s">
+        <v>186</v>
+      </c>
+      <c r="E64" t="s">
+        <v>35</v>
+      </c>
+      <c r="F64" s="1">
+        <v>46202</v>
+      </c>
+      <c r="G64" s="1">
+        <v>46210</v>
+      </c>
+      <c r="H64" s="43">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>-43</v>
+      </c>
+      <c r="J64" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>714</v>
+      </c>
+      <c r="B65" t="s">
+        <v>58</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="D65" t="s">
+        <v>186</v>
+      </c>
+      <c r="E65" t="s">
+        <v>681</v>
+      </c>
+      <c r="F65" s="1">
+        <v>46202</v>
+      </c>
+      <c r="G65" s="1">
+        <v>46205</v>
+      </c>
+      <c r="H65" s="43">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>-36</v>
+      </c>
+      <c r="J65" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>725</v>
+      </c>
+      <c r="B66" t="s">
+        <v>54</v>
+      </c>
+      <c r="C66">
+        <v>5</v>
+      </c>
+      <c r="D66" t="s">
+        <v>186</v>
+      </c>
+      <c r="E66" t="s">
+        <v>681</v>
+      </c>
+      <c r="F66" s="1">
+        <v>46202</v>
+      </c>
+      <c r="G66" s="1">
+        <v>46208</v>
+      </c>
+      <c r="H66" s="43">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>-31</v>
+      </c>
+      <c r="J66" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>205</v>
+      </c>
+      <c r="B67" t="s">
+        <v>196</v>
+      </c>
+      <c r="C67">
+        <v>6</v>
+      </c>
+      <c r="D67" t="s">
+        <v>186</v>
+      </c>
+      <c r="E67" t="s">
+        <v>35</v>
+      </c>
+      <c r="F67" s="1">
+        <v>46202</v>
+      </c>
+      <c r="G67" s="1">
+        <v>46209</v>
+      </c>
+      <c r="H67" s="43">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>-39</v>
+      </c>
+      <c r="J67" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>206</v>
+      </c>
+      <c r="B68" t="s">
+        <v>198</v>
+      </c>
+      <c r="C68">
+        <v>6</v>
+      </c>
+      <c r="D68" t="s">
+        <v>186</v>
+      </c>
+      <c r="E68" t="s">
+        <v>35</v>
+      </c>
+      <c r="F68" s="1">
+        <v>46202</v>
+      </c>
+      <c r="G68" s="1">
+        <v>46209</v>
+      </c>
+      <c r="H68" s="43">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>-35</v>
+      </c>
+      <c r="J68" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B69" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69">
+        <v>4</v>
+      </c>
+      <c r="D69" t="s">
+        <v>186</v>
+      </c>
+      <c r="E69" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F69" s="1">
+        <v>46203</v>
+      </c>
+      <c r="G69" s="1">
+        <v>46207</v>
+      </c>
+      <c r="H69" s="43">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>-22</v>
+      </c>
+      <c r="J69" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B70" t="s">
+        <v>58</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70" t="s">
+        <v>186</v>
+      </c>
+      <c r="E70" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F70" s="1">
+        <v>46203</v>
+      </c>
+      <c r="G70" s="1">
+        <v>46205</v>
+      </c>
+      <c r="H70" s="43">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>-50</v>
+      </c>
+      <c r="J70" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C71">
+        <v>10</v>
+      </c>
+      <c r="D71" t="s">
+        <v>186</v>
+      </c>
+      <c r="E71" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F71" s="1">
+        <v>46203</v>
+      </c>
+      <c r="G71" s="1">
+        <v>46214</v>
+      </c>
+      <c r="H71" s="43">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>-22</v>
+      </c>
+      <c r="J71" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>189</v>
+      </c>
+      <c r="B72" t="s">
+        <v>92</v>
+      </c>
+      <c r="C72">
+        <v>6</v>
+      </c>
+      <c r="D72" t="s">
+        <v>186</v>
+      </c>
+      <c r="E72" t="s">
+        <v>35</v>
+      </c>
+      <c r="F72" s="1">
+        <v>46203</v>
+      </c>
+      <c r="G72" s="1">
+        <v>46210</v>
+      </c>
+      <c r="H72" s="43">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>-43</v>
+      </c>
+      <c r="J72" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>705</v>
+      </c>
+      <c r="B73" t="s">
+        <v>69</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+      <c r="D73" t="s">
+        <v>186</v>
+      </c>
+      <c r="E73" t="s">
+        <v>681</v>
+      </c>
+      <c r="F73" s="1">
+        <v>46203</v>
+      </c>
+      <c r="G73" s="1">
+        <v>46205</v>
+      </c>
+      <c r="H73" s="43">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>-36</v>
+      </c>
+      <c r="J73" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B74" t="s">
+        <v>58</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+      <c r="D74" t="s">
+        <v>186</v>
+      </c>
+      <c r="E74" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F74" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G74" s="1">
+        <v>46205</v>
+      </c>
+      <c r="H74" s="43">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>8</v>
+      </c>
+      <c r="J74" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B75" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75">
+        <v>10</v>
+      </c>
+      <c r="D75" t="s">
+        <v>186</v>
+      </c>
+      <c r="E75" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F75" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G75" s="1">
+        <v>46215</v>
+      </c>
+      <c r="H75" s="43">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>74</v>
+      </c>
+      <c r="J75" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10013,7 +12464,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10023,10 +12474,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="42" t="s">
         <v>2232</v>
       </c>
-      <c r="B1" s="39"/>
+      <c r="B1" s="42"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
@@ -10202,7 +12653,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10339,10 +12790,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E6">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -88471,13 +90922,13 @@
         <f>B2-C2</f>
         <v>-62</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="40" t="s">
         <v>2296</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="40" t="s">
         <v>2298</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="41" t="s">
         <v>2299</v>
       </c>
     </row>
@@ -88495,7 +90946,7 @@
         <f t="shared" ref="D3:D6" si="0">B3-C3</f>
         <v>-54</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="40" t="s">
         <v>2139</v>
       </c>
       <c r="F3" s="16" t="s">
@@ -88519,13 +90970,13 @@
         <f t="shared" si="0"/>
         <v>-64</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="40" t="s">
         <v>2296</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="40" t="s">
         <v>2298</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="G4" s="41" t="s">
         <v>2299</v>
       </c>
     </row>
@@ -88543,10 +90994,10 @@
         <f t="shared" si="0"/>
         <v>-27</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="40" t="s">
         <v>2297</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="40" t="s">
         <v>2137</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -88578,22 +91029,22 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="39" t="s">
         <v>2278</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="39" t="s">
         <v>1711</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="39" t="s">
         <v>1711</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="39" t="s">
         <v>1711</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="39" t="s">
         <v>2279</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="39" t="s">
         <v>2280</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -88798,7 +91249,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="26.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="41" t="s">
         <v>2300</v>
       </c>
       <c r="B6" s="4" t="s">

--- a/data/project-dashboard.xlsx
+++ b/data/project-dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00-Maseel Project Control\11-Website Dashboard\Dynamic Web\project-dashboard-website\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB51AB52-382A-4DC3-A8EF-B22C0B9AF1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C99275-9546-4BE0-BB7C-A1EB5CC3ED47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project_Info" sheetId="1" r:id="rId1"/>
@@ -90913,14 +90913,14 @@
         <v>26</v>
       </c>
       <c r="B2" s="8">
-        <v>46476</v>
+        <v>46477</v>
       </c>
       <c r="C2" s="8">
         <v>46538</v>
       </c>
       <c r="D2" s="17">
         <f>B2-C2</f>
-        <v>-62</v>
+        <v>-61</v>
       </c>
       <c r="E2" s="40" t="s">
         <v>2296</v>
@@ -90937,14 +90937,14 @@
         <v>27</v>
       </c>
       <c r="B3" s="8">
-        <v>46475</v>
+        <v>46477</v>
       </c>
       <c r="C3" s="8">
         <v>46529</v>
       </c>
       <c r="D3" s="17">
         <f t="shared" ref="D3:D6" si="0">B3-C3</f>
-        <v>-54</v>
+        <v>-52</v>
       </c>
       <c r="E3" s="40" t="s">
         <v>2139</v>
@@ -90961,14 +90961,14 @@
         <v>28</v>
       </c>
       <c r="B4" s="8">
-        <v>46475</v>
+        <v>46477</v>
       </c>
       <c r="C4" s="8">
         <v>46539</v>
       </c>
       <c r="D4" s="17">
         <f t="shared" si="0"/>
-        <v>-64</v>
+        <v>-62</v>
       </c>
       <c r="E4" s="40" t="s">
         <v>2296</v>

--- a/data/project-dashboard.xlsx
+++ b/data/project-dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00-Maseel Project Control\11-Website Dashboard\Dynamic Web\project-dashboard-website\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C99275-9546-4BE0-BB7C-A1EB5CC3ED47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A59438-D051-4A3B-B570-ED2F11B31368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project_Info" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10440" uniqueCount="2308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10433" uniqueCount="2308">
   <si>
     <t>Project Name</t>
   </si>
@@ -7249,10 +7249,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -7261,15 +7261,6 @@
     <cellStyle name="Per cent" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="46">
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -7299,6 +7290,15 @@
           <bgColor rgb="FFF8CBAD"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
@@ -7431,30 +7431,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -7485,6 +7461,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
@@ -7495,14 +7481,28 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9420,17 +9420,17 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{63CF4BD0-58E1-4A31-B532-77FDF440E2C9}" name="Look_Ahead" displayName="Look_Ahead" ref="A1:J75" totalsRowShown="0">
-  <autoFilter ref="A1:J75" xr:uid="{63CF4BD0-58E1-4A31-B532-77FDF440E2C9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{63CF4BD0-58E1-4A31-B532-77FDF440E2C9}" name="Look_Ahead" displayName="Look_Ahead" ref="A1:J74" totalsRowShown="0">
+  <autoFilter ref="A1:J74" xr:uid="{63CF4BD0-58E1-4A31-B532-77FDF440E2C9}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{057A596C-1792-405A-90C5-8318C14D4D97}" name="Activity ID"/>
     <tableColumn id="2" xr3:uid="{1E3CDF14-2CB8-4DEF-9547-89E06C85CFF9}" name="Activity Name"/>
     <tableColumn id="3" xr3:uid="{BEBE23B0-DD9A-46A0-83F0-F7AADFB113E0}" name="Original Duration"/>
     <tableColumn id="4" xr3:uid="{6FF22079-BD1C-473D-8452-4351A338CF7F}" name="Activity Status"/>
     <tableColumn id="5" xr3:uid="{07E5DDBB-1EE3-4BBE-A76E-96D7AC3BF882}" name="02- Con.Phase"/>
-    <tableColumn id="6" xr3:uid="{551887B7-0CF0-4401-9C1A-2DF3FF831FD4}" name="Start" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{947F443A-6D45-4251-B1BF-9CBC39B7A1B5}" name="Finish" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{62C03662-69E1-4727-A2DD-0879099C639A}" name="Performance % Complete" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{551887B7-0CF0-4401-9C1A-2DF3FF831FD4}" name="Start" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{947F443A-6D45-4251-B1BF-9CBC39B7A1B5}" name="Finish" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{62C03662-69E1-4727-A2DD-0879099C639A}" name="Performance % Complete" dataDxfId="3"/>
     <tableColumn id="9" xr3:uid="{5C1834A0-CE32-4342-8EF5-1EC543B01FAA}" name="Total Float"/>
     <tableColumn id="10" xr3:uid="{0293C0C3-272F-4BB3-B63E-9D3BC97471CF}" name="Critical"/>
   </tableColumns>
@@ -9460,13 +9460,13 @@
     <tableColumn id="4" xr3:uid="{26228A24-7B89-4F53-8C02-895BDE96807E}" name="Variance %">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{043BEE59-9BB9-48CA-BCAF-B0B49AB502E6}" name="SPI" dataDxfId="43">
+    <tableColumn id="5" xr3:uid="{043BEE59-9BB9-48CA-BCAF-B0B49AB502E6}" name="SPI" dataDxfId="37">
       <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{7FA7C1AA-84AA-4AEE-BAFB-D3FAEE25A5D8}" name="BL Start Date"/>
     <tableColumn id="7" xr3:uid="{4234B7FF-F64E-4A3A-9F37-5B5BEF6D9017}" name="BL Finish Date"/>
     <tableColumn id="8" xr3:uid="{3B605CB7-AB94-4F24-892D-8D23051F549D}" name="Forecast Finish Date"/>
-    <tableColumn id="9" xr3:uid="{8627A771-209F-4934-998C-3A0C21C0CC0E}" name="Variance Finish Date" dataDxfId="42">
+    <tableColumn id="9" xr3:uid="{8627A771-209F-4934-998C-3A0C21C0CC0E}" name="Variance Finish Date" dataDxfId="36">
       <calculatedColumnFormula>G2-H2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{E446F1CD-F15A-4A57-924F-E08331EF6928}" name="Project Duration"/>
@@ -9476,7 +9476,7 @@
     <tableColumn id="12" xr3:uid="{C8177739-B2D6-445C-909A-3B630381521D}" name="Remaining Time">
       <calculatedColumnFormula>J2-K2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{2413F253-FC61-4728-AA12-82814EB1AC1E}" name="Time Elapsed %" dataDxfId="41">
+    <tableColumn id="13" xr3:uid="{2413F253-FC61-4728-AA12-82814EB1AC1E}" name="Time Elapsed %" dataDxfId="35">
       <calculatedColumnFormula>K2/J2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9490,10 +9490,10 @@
     <tableColumn id="1" xr3:uid="{5CC08CFD-BB32-42AE-8929-3D92342465CF}" name="Phase"/>
     <tableColumn id="2" xr3:uid="{5D73634F-CCC4-411A-8B1A-98488EA6FA8F}" name="Planned %"/>
     <tableColumn id="3" xr3:uid="{32C402C6-661D-4391-B7B2-C3C85BB5AF80}" name="Actual %"/>
-    <tableColumn id="4" xr3:uid="{089AD09E-CE81-45D7-9664-49ACA4EE345D}" name="Variance" dataDxfId="45">
+    <tableColumn id="4" xr3:uid="{089AD09E-CE81-45D7-9664-49ACA4EE345D}" name="Variance" dataDxfId="34">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FA9B9069-F615-43F7-AF56-68E6B97329D8}" name="SPI" dataDxfId="44">
+    <tableColumn id="5" xr3:uid="{FA9B9069-F615-43F7-AF56-68E6B97329D8}" name="SPI" dataDxfId="33">
       <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9509,29 +9509,29 @@
     <tableColumn id="3" xr3:uid="{EEFE8DE6-C657-48D9-88FA-7D5A43C1590A}" name="Original Duration"/>
     <tableColumn id="4" xr3:uid="{BFD618A5-3D3D-4C62-9AEE-667429FF6625}" name="Activity Status"/>
     <tableColumn id="5" xr3:uid="{54C85E9C-40B3-4A27-A7A1-08D5632ACFD5}" name="02- Con.Phase"/>
-    <tableColumn id="6" xr3:uid="{1E54E21F-3570-4379-98B5-D3F79BAD2A54}" name="BL Project Start" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{8AF72BC8-3D95-4695-BE78-28DE430A0C96}" name="BL Project Finish" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{41D5B848-CED1-4B85-B7C0-0C2EEADFA08F}" name="Start" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{6993DFB5-C059-4A89-9ABD-71F49C2A6F74}" name="Finish" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{9EAC2262-2A27-42A8-BB73-73F39AFC4912}" name="Schedule % Complete" dataDxfId="36" dataCellStyle="Per cent"/>
-    <tableColumn id="11" xr3:uid="{B218F782-EF65-4945-9E84-E0A88975643B}" name="Performance % Complete" dataDxfId="35" dataCellStyle="Per cent"/>
-    <tableColumn id="12" xr3:uid="{85C93BA9-907D-4549-9ECD-E1601A6B8FF1}" name="Total Float" dataDxfId="34"/>
-    <tableColumn id="13" xr3:uid="{C49B17F2-109E-42EB-814F-75ABCAF72ADF}" name="Critical" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{1E54E21F-3570-4379-98B5-D3F79BAD2A54}" name="BL Project Start" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{8AF72BC8-3D95-4695-BE78-28DE430A0C96}" name="BL Project Finish" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{41D5B848-CED1-4B85-B7C0-0C2EEADFA08F}" name="Start" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{6993DFB5-C059-4A89-9ABD-71F49C2A6F74}" name="Finish" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{9EAC2262-2A27-42A8-BB73-73F39AFC4912}" name="Schedule % Complete" dataDxfId="28" dataCellStyle="Per cent"/>
+    <tableColumn id="11" xr3:uid="{B218F782-EF65-4945-9E84-E0A88975643B}" name="Performance % Complete" dataDxfId="27" dataCellStyle="Per cent"/>
+    <tableColumn id="12" xr3:uid="{85C93BA9-907D-4549-9ECD-E1601A6B8FF1}" name="Total Float" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{C49B17F2-109E-42EB-814F-75ABCAF72ADF}" name="Critical" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{646BB870-B00C-435D-A3B9-FC5EE922B49E}" name="DelaysTable16" displayName="DelaysTable16" ref="A1:G7" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{646BB870-B00C-435D-A3B9-FC5EE922B49E}" name="DelaysTable16" displayName="DelaysTable16" ref="A1:G7" dataDxfId="45">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{432610E1-EB61-4ACD-97A4-8A63654F84F9}" name="Phase Delay/Ahead" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{2C5412A7-92CE-4EAC-8330-FA329E02B968}" name="BL Finish Date" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{0E5F2071-69D2-4243-B28B-C06740FB7648}" name="Forecast Finish Date" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{E02C79E2-295D-4560-9843-63A6C0451E21}" name="Variance Finish Date" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{5A1277A0-CB8F-43B1-BC65-D584276375E2}" name="Delay Reason" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{3E4DC573-6186-4CC7-8D6B-0A44D59D4182}" name="Recovery Action" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{C16296EE-BD20-4329-86E5-BA92EF668C0A}" name="Responsible" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{432610E1-EB61-4ACD-97A4-8A63654F84F9}" name="Phase Delay/Ahead" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{2C5412A7-92CE-4EAC-8330-FA329E02B968}" name="BL Finish Date" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{0E5F2071-69D2-4243-B28B-C06740FB7648}" name="Forecast Finish Date" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{E02C79E2-295D-4560-9843-63A6C0451E21}" name="Variance Finish Date" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{5A1277A0-CB8F-43B1-BC65-D584276375E2}" name="Delay Reason" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{3E4DC573-6186-4CC7-8D6B-0A44D59D4182}" name="Recovery Action" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{C16296EE-BD20-4329-86E5-BA92EF668C0A}" name="Responsible" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9855,7 +9855,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD8E641E-8ADA-437C-9106-D96C97500733}">
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
@@ -9923,7 +9923,7 @@
       <c r="G2" s="1">
         <v>46186</v>
       </c>
-      <c r="H2" s="43">
+      <c r="H2" s="42">
         <v>0.99</v>
       </c>
       <c r="I2">
@@ -9955,7 +9955,7 @@
       <c r="G3" s="1">
         <v>46187</v>
       </c>
-      <c r="H3" s="43">
+      <c r="H3" s="42">
         <v>0.91</v>
       </c>
       <c r="I3">
@@ -9987,7 +9987,7 @@
       <c r="G4" s="1">
         <v>46184</v>
       </c>
-      <c r="H4" s="43">
+      <c r="H4" s="42">
         <v>0.99</v>
       </c>
       <c r="I4">
@@ -10019,7 +10019,7 @@
       <c r="G5" s="1">
         <v>46184</v>
       </c>
-      <c r="H5" s="43">
+      <c r="H5" s="42">
         <v>0.95</v>
       </c>
       <c r="I5">
@@ -10051,7 +10051,7 @@
       <c r="G6" s="1">
         <v>46184</v>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="42">
         <v>0.95</v>
       </c>
       <c r="I6">
@@ -10083,7 +10083,7 @@
       <c r="G7" s="1">
         <v>46184</v>
       </c>
-      <c r="H7" s="43">
+      <c r="H7" s="42">
         <v>0.95</v>
       </c>
       <c r="I7">
@@ -10115,7 +10115,7 @@
       <c r="G8" s="1">
         <v>46188</v>
       </c>
-      <c r="H8" s="43">
+      <c r="H8" s="42">
         <v>0.9</v>
       </c>
       <c r="I8">
@@ -10127,42 +10127,45 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1189</v>
+        <v>1968</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="C9">
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>1139</v>
+        <v>1941</v>
       </c>
       <c r="F9" t="s">
-        <v>1190</v>
-      </c>
-      <c r="G9" t="s">
-        <v>2292</v>
-      </c>
-      <c r="H9" s="43">
-        <v>1</v>
+        <v>1961</v>
+      </c>
+      <c r="G9" s="1">
+        <v>46202</v>
+      </c>
+      <c r="H9" s="42">
+        <v>0.05</v>
+      </c>
+      <c r="I9">
+        <v>-50</v>
       </c>
       <c r="J9" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1968</v>
+        <v>1960</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
         <v>98</v>
@@ -10174,13 +10177,13 @@
         <v>1961</v>
       </c>
       <c r="G10" s="1">
-        <v>46202</v>
-      </c>
-      <c r="H10" s="43">
-        <v>0.05</v>
+        <v>46188</v>
+      </c>
+      <c r="H10" s="42">
+        <v>0.9</v>
       </c>
       <c r="I10">
-        <v>-50</v>
+        <v>-35</v>
       </c>
       <c r="J10" t="s">
         <v>2284</v>
@@ -10188,31 +10191,31 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1960</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
         <v>98</v>
       </c>
       <c r="E11" t="s">
-        <v>1941</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>1961</v>
+        <v>149</v>
       </c>
       <c r="G11" s="1">
-        <v>46188</v>
-      </c>
-      <c r="H11" s="43">
-        <v>0.9</v>
+        <v>46193</v>
+      </c>
+      <c r="H11" s="42">
+        <v>0.95</v>
       </c>
       <c r="I11">
-        <v>-35</v>
+        <v>-25</v>
       </c>
       <c r="J11" t="s">
         <v>2284</v>
@@ -10220,31 +10223,31 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>148</v>
+        <v>1962</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
         <v>98</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>1941</v>
       </c>
       <c r="F12" t="s">
-        <v>149</v>
+        <v>1149</v>
       </c>
       <c r="G12" s="1">
         <v>46193</v>
       </c>
-      <c r="H12" s="43">
-        <v>0.95</v>
+      <c r="H12" s="42">
+        <v>0.9</v>
       </c>
       <c r="I12">
-        <v>-25</v>
+        <v>-35</v>
       </c>
       <c r="J12" t="s">
         <v>2284</v>
@@ -10252,31 +10255,31 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1962</v>
+        <v>1700</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>1701</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
         <v>98</v>
       </c>
       <c r="E13" t="s">
-        <v>1941</v>
+        <v>1690</v>
       </c>
       <c r="F13" t="s">
-        <v>1149</v>
+        <v>1702</v>
       </c>
       <c r="G13" s="1">
-        <v>46193</v>
-      </c>
-      <c r="H13" s="43">
-        <v>0.9</v>
+        <v>46191</v>
+      </c>
+      <c r="H13" s="42">
+        <v>0.96</v>
       </c>
       <c r="I13">
-        <v>-35</v>
+        <v>-22</v>
       </c>
       <c r="J13" t="s">
         <v>2284</v>
@@ -10284,31 +10287,31 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1700</v>
+        <v>95</v>
       </c>
       <c r="B14" t="s">
-        <v>1701</v>
+        <v>96</v>
       </c>
       <c r="C14">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="D14" t="s">
         <v>98</v>
       </c>
       <c r="E14" t="s">
-        <v>1690</v>
+        <v>35</v>
       </c>
       <c r="F14" t="s">
-        <v>1702</v>
+        <v>97</v>
       </c>
       <c r="G14" s="1">
-        <v>46191</v>
-      </c>
-      <c r="H14" s="43">
-        <v>0.96</v>
+        <v>46187</v>
+      </c>
+      <c r="H14" s="42">
+        <v>0.95</v>
       </c>
       <c r="I14">
-        <v>-22</v>
+        <v>-41</v>
       </c>
       <c r="J14" t="s">
         <v>2284</v>
@@ -10316,7 +10319,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="B15" t="s">
         <v>96</v>
@@ -10331,16 +10334,16 @@
         <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="G15" s="1">
-        <v>46187</v>
-      </c>
-      <c r="H15" s="43">
-        <v>0.95</v>
+        <v>46196</v>
+      </c>
+      <c r="H15" s="42">
+        <v>0.6</v>
       </c>
       <c r="I15">
-        <v>-41</v>
+        <v>-25</v>
       </c>
       <c r="J15" t="s">
         <v>2284</v>
@@ -10348,31 +10351,31 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>150</v>
+        <v>1963</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D16" t="s">
         <v>98</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>1941</v>
       </c>
       <c r="F16" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="G16" s="1">
-        <v>46196</v>
-      </c>
-      <c r="H16" s="43">
+        <v>46203</v>
+      </c>
+      <c r="H16" s="42">
         <v>0.6</v>
       </c>
       <c r="I16">
-        <v>-25</v>
+        <v>-35</v>
       </c>
       <c r="J16" t="s">
         <v>2284</v>
@@ -10380,31 +10383,31 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1963</v>
+        <v>1162</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C17">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D17" t="s">
         <v>98</v>
       </c>
       <c r="E17" t="s">
-        <v>1941</v>
+        <v>1139</v>
       </c>
       <c r="F17" t="s">
-        <v>94</v>
+        <v>167</v>
       </c>
       <c r="G17" s="1">
-        <v>46203</v>
-      </c>
-      <c r="H17" s="43">
-        <v>0.6</v>
+        <v>46189</v>
+      </c>
+      <c r="H17" s="42">
+        <v>0.9</v>
       </c>
       <c r="I17">
-        <v>-35</v>
+        <v>-39</v>
       </c>
       <c r="J17" t="s">
         <v>2284</v>
@@ -10412,13 +10415,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1162</v>
+        <v>1191</v>
       </c>
       <c r="B18" t="s">
         <v>96</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" t="s">
         <v>98</v>
@@ -10427,16 +10430,16 @@
         <v>1139</v>
       </c>
       <c r="F18" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="G18" s="1">
-        <v>46189</v>
-      </c>
-      <c r="H18" s="43">
+        <v>46187</v>
+      </c>
+      <c r="H18" s="42">
         <v>0.9</v>
       </c>
       <c r="I18">
-        <v>-39</v>
+        <v>-15</v>
       </c>
       <c r="J18" t="s">
         <v>2284</v>
@@ -10444,7 +10447,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1191</v>
+        <v>171</v>
       </c>
       <c r="B19" t="s">
         <v>96</v>
@@ -10456,19 +10459,19 @@
         <v>98</v>
       </c>
       <c r="E19" t="s">
-        <v>1139</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="G19" s="1">
         <v>46187</v>
       </c>
-      <c r="H19" s="43">
-        <v>0.9</v>
+      <c r="H19" s="42">
+        <v>0.7</v>
       </c>
       <c r="I19">
-        <v>-15</v>
+        <v>-26</v>
       </c>
       <c r="J19" t="s">
         <v>2284</v>
@@ -10476,31 +10479,31 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>171</v>
+        <v>1951</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" t="s">
         <v>98</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>1941</v>
       </c>
       <c r="F20" t="s">
         <v>172</v>
       </c>
       <c r="G20" s="1">
-        <v>46187</v>
-      </c>
-      <c r="H20" s="43">
-        <v>0.7</v>
+        <v>46195</v>
+      </c>
+      <c r="H20" s="42">
+        <v>0.3</v>
       </c>
       <c r="I20">
-        <v>-26</v>
+        <v>-50</v>
       </c>
       <c r="J20" t="s">
         <v>2284</v>
@@ -10508,31 +10511,31 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1951</v>
+        <v>688</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" t="s">
         <v>98</v>
       </c>
       <c r="E21" t="s">
-        <v>1941</v>
+        <v>681</v>
       </c>
       <c r="F21" t="s">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="G21" s="1">
-        <v>46195</v>
-      </c>
-      <c r="H21" s="43">
-        <v>0.3</v>
+        <v>46187</v>
+      </c>
+      <c r="H21" s="42">
+        <v>0.95</v>
       </c>
       <c r="I21">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="J21" t="s">
         <v>2284</v>
@@ -10540,28 +10543,28 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>688</v>
+        <v>191</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>192</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" t="s">
         <v>98</v>
       </c>
       <c r="E22" t="s">
-        <v>681</v>
+        <v>35</v>
       </c>
       <c r="F22" t="s">
-        <v>127</v>
+        <v>2277</v>
       </c>
       <c r="G22" s="1">
-        <v>46187</v>
-      </c>
-      <c r="H22" s="43">
-        <v>0.95</v>
+        <v>46194</v>
+      </c>
+      <c r="H22" s="42">
+        <v>0.35</v>
       </c>
       <c r="I22">
         <v>-40</v>
@@ -10572,28 +10575,28 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>191</v>
+        <v>689</v>
       </c>
       <c r="B23" t="s">
-        <v>192</v>
+        <v>54</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
         <v>98</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>681</v>
       </c>
       <c r="F23" t="s">
         <v>2277</v>
       </c>
       <c r="G23" s="1">
-        <v>46194</v>
-      </c>
-      <c r="H23" s="43">
-        <v>0.35</v>
+        <v>46190</v>
+      </c>
+      <c r="H23" s="42">
+        <v>0.7</v>
       </c>
       <c r="I23">
         <v>-40</v>
@@ -10604,31 +10607,31 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>689</v>
+        <v>1949</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>686</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D24" t="s">
         <v>98</v>
       </c>
       <c r="E24" t="s">
-        <v>681</v>
+        <v>1941</v>
       </c>
       <c r="F24" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="G24" s="1">
-        <v>46190</v>
-      </c>
-      <c r="H24" s="43">
-        <v>0.7</v>
+        <v>46188</v>
+      </c>
+      <c r="H24" s="42">
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="J24" t="s">
         <v>2284</v>
@@ -10636,31 +10639,31 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1949</v>
+        <v>701</v>
       </c>
       <c r="B25" t="s">
-        <v>686</v>
+        <v>54</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D25" t="s">
         <v>98</v>
       </c>
       <c r="E25" t="s">
-        <v>1941</v>
+        <v>681</v>
       </c>
       <c r="F25" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="G25" s="1">
-        <v>46188</v>
-      </c>
-      <c r="H25" s="43">
-        <v>0</v>
+        <v>46196</v>
+      </c>
+      <c r="H25" s="42">
+        <v>0.7</v>
       </c>
       <c r="I25">
-        <v>-50</v>
+        <v>-36</v>
       </c>
       <c r="J25" t="s">
         <v>2284</v>
@@ -10668,31 +10671,31 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>701</v>
+        <v>193</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>194</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
         <v>98</v>
       </c>
       <c r="E26" t="s">
-        <v>681</v>
+        <v>35</v>
       </c>
       <c r="F26" t="s">
-        <v>2275</v>
+        <v>2291</v>
       </c>
       <c r="G26" s="1">
-        <v>46196</v>
-      </c>
-      <c r="H26" s="43">
-        <v>0.7</v>
+        <v>46194</v>
+      </c>
+      <c r="H26" s="42">
+        <v>0.1</v>
       </c>
       <c r="I26">
-        <v>-36</v>
+        <v>-41</v>
       </c>
       <c r="J26" t="s">
         <v>2284</v>
@@ -10700,10 +10703,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B27" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C27">
         <v>6</v>
@@ -10715,16 +10718,16 @@
         <v>35</v>
       </c>
       <c r="F27" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="G27" s="1">
-        <v>46194</v>
-      </c>
-      <c r="H27" s="43">
+        <v>46197</v>
+      </c>
+      <c r="H27" s="42">
         <v>0.1</v>
       </c>
       <c r="I27">
-        <v>-41</v>
+        <v>-40</v>
       </c>
       <c r="J27" t="s">
         <v>2284</v>
@@ -10732,19 +10735,19 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>195</v>
+        <v>1240</v>
       </c>
       <c r="B28" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
         <v>98</v>
       </c>
       <c r="E28" t="s">
-        <v>35</v>
+        <v>1139</v>
       </c>
       <c r="F28" t="s">
         <v>2293</v>
@@ -10752,11 +10755,11 @@
       <c r="G28" s="1">
         <v>46197</v>
       </c>
-      <c r="H28" s="43">
-        <v>0.1</v>
+      <c r="H28" s="42">
+        <v>0.05</v>
       </c>
       <c r="I28">
-        <v>-40</v>
+        <v>-39</v>
       </c>
       <c r="J28" t="s">
         <v>2284</v>
@@ -10764,31 +10767,31 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1240</v>
+        <v>203</v>
       </c>
       <c r="B29" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="E29" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F29" t="s">
-        <v>2293</v>
+        <v>35</v>
+      </c>
+      <c r="F29" s="1">
+        <v>46184</v>
       </c>
       <c r="G29" s="1">
-        <v>46197</v>
-      </c>
-      <c r="H29" s="43">
-        <v>0.05</v>
+        <v>46190</v>
+      </c>
+      <c r="H29" s="42">
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>-39</v>
+        <v>-27</v>
       </c>
       <c r="J29" t="s">
         <v>2284</v>
@@ -10796,10 +10799,10 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C30">
         <v>6</v>
@@ -10816,11 +10819,11 @@
       <c r="G30" s="1">
         <v>46190</v>
       </c>
-      <c r="H30" s="43">
+      <c r="H30" s="42">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>-27</v>
+        <v>-23</v>
       </c>
       <c r="J30" t="s">
         <v>2284</v>
@@ -10828,10 +10831,10 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="B31" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C31">
         <v>6</v>
@@ -10843,16 +10846,16 @@
         <v>35</v>
       </c>
       <c r="F31" s="1">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="G31" s="1">
-        <v>46190</v>
-      </c>
-      <c r="H31" s="43">
+        <v>46194</v>
+      </c>
+      <c r="H31" s="42">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>-23</v>
+        <v>-26</v>
       </c>
       <c r="J31" t="s">
         <v>2284</v>
@@ -10860,31 +10863,31 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>215</v>
+        <v>1950</v>
       </c>
       <c r="B32" t="s">
-        <v>192</v>
+        <v>684</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D32" t="s">
         <v>186</v>
       </c>
       <c r="E32" t="s">
-        <v>35</v>
+        <v>1941</v>
       </c>
       <c r="F32" s="1">
         <v>46188</v>
       </c>
       <c r="G32" s="1">
-        <v>46194</v>
-      </c>
-      <c r="H32" s="43">
+        <v>46188</v>
+      </c>
+      <c r="H32" s="42">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>-26</v>
+        <v>-50</v>
       </c>
       <c r="J32" t="s">
         <v>2284</v>
@@ -10892,31 +10895,31 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1950</v>
+        <v>216</v>
       </c>
       <c r="B33" t="s">
-        <v>684</v>
+        <v>194</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D33" t="s">
         <v>186</v>
       </c>
       <c r="E33" t="s">
-        <v>1941</v>
+        <v>35</v>
       </c>
       <c r="F33" s="1">
         <v>46188</v>
       </c>
       <c r="G33" s="1">
-        <v>46188</v>
-      </c>
-      <c r="H33" s="43">
+        <v>46194</v>
+      </c>
+      <c r="H33" s="42">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>-50</v>
+        <v>-24</v>
       </c>
       <c r="J33" t="s">
         <v>2284</v>
@@ -10924,13 +10927,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="B34" t="s">
-        <v>194</v>
+        <v>81</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D34" t="s">
         <v>186</v>
@@ -10942,13 +10945,13 @@
         <v>46188</v>
       </c>
       <c r="G34" s="1">
-        <v>46194</v>
-      </c>
-      <c r="H34" s="43">
+        <v>46198</v>
+      </c>
+      <c r="H34" s="42">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>-24</v>
+        <v>-43</v>
       </c>
       <c r="J34" t="s">
         <v>2284</v>
@@ -10956,31 +10959,31 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>185</v>
+        <v>1703</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>1704</v>
       </c>
       <c r="C35">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
         <v>186</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>1690</v>
       </c>
       <c r="F35" s="1">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="G35" s="1">
-        <v>46198</v>
-      </c>
-      <c r="H35" s="43">
+        <v>46202</v>
+      </c>
+      <c r="H35" s="42">
         <v>0</v>
       </c>
       <c r="I35">
-        <v>-43</v>
+        <v>-22</v>
       </c>
       <c r="J35" t="s">
         <v>2284</v>
@@ -10988,31 +10991,31 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1703</v>
+        <v>217</v>
       </c>
       <c r="B36" t="s">
-        <v>1704</v>
+        <v>196</v>
       </c>
       <c r="C36">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D36" t="s">
         <v>186</v>
       </c>
       <c r="E36" t="s">
-        <v>1690</v>
+        <v>35</v>
       </c>
       <c r="F36" s="1">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="G36" s="1">
-        <v>46202</v>
-      </c>
-      <c r="H36" s="43">
+        <v>46196</v>
+      </c>
+      <c r="H36" s="42">
         <v>0</v>
       </c>
       <c r="I36">
-        <v>-22</v>
+        <v>-26</v>
       </c>
       <c r="J36" t="s">
         <v>2284</v>
@@ -11020,31 +11023,31 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>217</v>
+        <v>690</v>
       </c>
       <c r="B37" t="s">
-        <v>196</v>
+        <v>58</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D37" t="s">
         <v>186</v>
       </c>
       <c r="E37" t="s">
-        <v>35</v>
+        <v>681</v>
       </c>
       <c r="F37" s="1">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="G37" s="1">
-        <v>46196</v>
-      </c>
-      <c r="H37" s="43">
+        <v>46195</v>
+      </c>
+      <c r="H37" s="42">
         <v>0</v>
       </c>
       <c r="I37">
-        <v>-26</v>
+        <v>-41</v>
       </c>
       <c r="J37" t="s">
         <v>2284</v>
@@ -11052,27 +11055,27 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>690</v>
+        <v>197</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>198</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D38" t="s">
         <v>186</v>
       </c>
       <c r="E38" t="s">
-        <v>681</v>
+        <v>35</v>
       </c>
       <c r="F38" s="1">
-        <v>46191</v>
+        <v>46193</v>
       </c>
       <c r="G38" s="1">
-        <v>46195</v>
-      </c>
-      <c r="H38" s="43">
+        <v>46198</v>
+      </c>
+      <c r="H38" s="42">
         <v>0</v>
       </c>
       <c r="I38">
@@ -11084,10 +11087,10 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="B39" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C39">
         <v>6</v>
@@ -11104,11 +11107,11 @@
       <c r="G39" s="1">
         <v>46198</v>
       </c>
-      <c r="H39" s="43">
+      <c r="H39" s="42">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>-41</v>
+        <v>-24</v>
       </c>
       <c r="J39" t="s">
         <v>2284</v>
@@ -11116,45 +11119,45 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>218</v>
+        <v>1207</v>
       </c>
       <c r="B40" t="s">
-        <v>219</v>
+        <v>54</v>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D40" t="s">
         <v>186</v>
       </c>
       <c r="E40" t="s">
-        <v>35</v>
+        <v>1139</v>
       </c>
       <c r="F40" s="1">
         <v>46193</v>
       </c>
       <c r="G40" s="1">
-        <v>46198</v>
-      </c>
-      <c r="H40" s="43">
+        <v>46203</v>
+      </c>
+      <c r="H40" s="42">
         <v>0</v>
       </c>
       <c r="I40">
-        <v>-24</v>
+        <v>8</v>
       </c>
       <c r="J40" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1207</v>
+        <v>1241</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D41" t="s">
         <v>186</v>
@@ -11163,48 +11166,48 @@
         <v>1139</v>
       </c>
       <c r="F41" s="1">
-        <v>46193</v>
+        <v>46195</v>
       </c>
       <c r="G41" s="1">
-        <v>46203</v>
-      </c>
-      <c r="H41" s="43">
+        <v>46202</v>
+      </c>
+      <c r="H41" s="42">
         <v>0</v>
       </c>
       <c r="I41">
-        <v>8</v>
+        <v>-39</v>
       </c>
       <c r="J41" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1241</v>
+        <v>1952</v>
       </c>
       <c r="B42" t="s">
-        <v>198</v>
+        <v>43</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D42" t="s">
         <v>186</v>
       </c>
       <c r="E42" t="s">
-        <v>1139</v>
+        <v>1941</v>
       </c>
       <c r="F42" s="1">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="G42" s="1">
-        <v>46202</v>
-      </c>
-      <c r="H42" s="43">
+        <v>46198</v>
+      </c>
+      <c r="H42" s="42">
         <v>0</v>
       </c>
       <c r="I42">
-        <v>-39</v>
+        <v>-50</v>
       </c>
       <c r="J42" t="s">
         <v>2284</v>
@@ -11212,10 +11215,10 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1952</v>
+        <v>691</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -11224,7 +11227,7 @@
         <v>186</v>
       </c>
       <c r="E43" t="s">
-        <v>1941</v>
+        <v>681</v>
       </c>
       <c r="F43" s="1">
         <v>46196</v>
@@ -11232,11 +11235,11 @@
       <c r="G43" s="1">
         <v>46198</v>
       </c>
-      <c r="H43" s="43">
+      <c r="H43" s="42">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>-50</v>
+        <v>-41</v>
       </c>
       <c r="J43" t="s">
         <v>2284</v>
@@ -11244,10 +11247,10 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C44">
         <v>3</v>
@@ -11262,13 +11265,13 @@
         <v>46196</v>
       </c>
       <c r="G44" s="1">
-        <v>46198</v>
-      </c>
-      <c r="H44" s="43">
+        <v>46200</v>
+      </c>
+      <c r="H44" s="42">
         <v>0</v>
       </c>
       <c r="I44">
-        <v>-41</v>
+        <v>-36</v>
       </c>
       <c r="J44" t="s">
         <v>2284</v>
@@ -11276,13 +11279,13 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D45" t="s">
         <v>186</v>
@@ -11294,9 +11297,9 @@
         <v>46196</v>
       </c>
       <c r="G45" s="1">
-        <v>46200</v>
-      </c>
-      <c r="H45" s="43">
+        <v>46202</v>
+      </c>
+      <c r="H45" s="42">
         <v>0</v>
       </c>
       <c r="I45">
@@ -11308,31 +11311,31 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>713</v>
+        <v>209</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D46" t="s">
         <v>186</v>
       </c>
       <c r="E46" t="s">
-        <v>681</v>
+        <v>35</v>
       </c>
       <c r="F46" s="1">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="G46" s="1">
-        <v>46202</v>
-      </c>
-      <c r="H46" s="43">
+        <v>46203</v>
+      </c>
+      <c r="H46" s="42">
         <v>0</v>
       </c>
       <c r="I46">
-        <v>-36</v>
+        <v>-25</v>
       </c>
       <c r="J46" t="s">
         <v>2284</v>
@@ -11340,13 +11343,13 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B47" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C47">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D47" t="s">
         <v>186</v>
@@ -11358,13 +11361,13 @@
         <v>46197</v>
       </c>
       <c r="G47" s="1">
-        <v>46203</v>
-      </c>
-      <c r="H47" s="43">
+        <v>46197</v>
+      </c>
+      <c r="H47" s="42">
         <v>0</v>
       </c>
       <c r="I47">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="J47" t="s">
         <v>2284</v>
@@ -11372,13 +11375,13 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B48" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D48" t="s">
         <v>186</v>
@@ -11390,13 +11393,13 @@
         <v>46197</v>
       </c>
       <c r="G48" s="1">
-        <v>46197</v>
-      </c>
-      <c r="H48" s="43">
+        <v>46203</v>
+      </c>
+      <c r="H48" s="42">
         <v>0</v>
       </c>
       <c r="I48">
-        <v>-26</v>
+        <v>-22</v>
       </c>
       <c r="J48" t="s">
         <v>2284</v>
@@ -11404,13 +11407,13 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B49" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D49" t="s">
         <v>186</v>
@@ -11419,16 +11422,16 @@
         <v>35</v>
       </c>
       <c r="F49" s="1">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="G49" s="1">
-        <v>46203</v>
-      </c>
-      <c r="H49" s="43">
+        <v>46198</v>
+      </c>
+      <c r="H49" s="42">
         <v>0</v>
       </c>
       <c r="I49">
-        <v>-22</v>
+        <v>-40</v>
       </c>
       <c r="J49" t="s">
         <v>2284</v>
@@ -11436,13 +11439,13 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B50" t="s">
-        <v>200</v>
+        <v>84</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D50" t="s">
         <v>186</v>
@@ -11454,13 +11457,13 @@
         <v>46198</v>
       </c>
       <c r="G50" s="1">
-        <v>46198</v>
-      </c>
-      <c r="H50" s="43">
+        <v>46205</v>
+      </c>
+      <c r="H50" s="42">
         <v>0</v>
       </c>
       <c r="I50">
-        <v>-40</v>
+        <v>-43</v>
       </c>
       <c r="J50" t="s">
         <v>2284</v>
@@ -11468,13 +11471,13 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D51" t="s">
         <v>186</v>
@@ -11483,16 +11486,16 @@
         <v>35</v>
       </c>
       <c r="F51" s="1">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="G51" s="1">
-        <v>46205</v>
-      </c>
-      <c r="H51" s="43">
+        <v>46202</v>
+      </c>
+      <c r="H51" s="42">
         <v>0</v>
       </c>
       <c r="I51">
-        <v>-43</v>
+        <v>-41</v>
       </c>
       <c r="J51" t="s">
         <v>2284</v>
@@ -11500,7 +11503,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="B52" t="s">
         <v>202</v>
@@ -11520,11 +11523,11 @@
       <c r="G52" s="1">
         <v>46202</v>
       </c>
-      <c r="H52" s="43">
+      <c r="H52" s="42">
         <v>0</v>
       </c>
       <c r="I52">
-        <v>-41</v>
+        <v>-24</v>
       </c>
       <c r="J52" t="s">
         <v>2284</v>
@@ -11532,31 +11535,31 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>221</v>
+        <v>1243</v>
       </c>
       <c r="B53" t="s">
         <v>202</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D53" t="s">
         <v>186</v>
       </c>
       <c r="E53" t="s">
-        <v>35</v>
+        <v>1139</v>
       </c>
       <c r="F53" s="1">
         <v>46200</v>
       </c>
       <c r="G53" s="1">
-        <v>46202</v>
-      </c>
-      <c r="H53" s="43">
+        <v>46207</v>
+      </c>
+      <c r="H53" s="42">
         <v>0</v>
       </c>
       <c r="I53">
-        <v>-24</v>
+        <v>-39</v>
       </c>
       <c r="J53" t="s">
         <v>2284</v>
@@ -11564,31 +11567,31 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1243</v>
+        <v>693</v>
       </c>
       <c r="B54" t="s">
-        <v>202</v>
+        <v>69</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D54" t="s">
         <v>186</v>
       </c>
       <c r="E54" t="s">
-        <v>1139</v>
+        <v>681</v>
       </c>
       <c r="F54" s="1">
         <v>46200</v>
       </c>
       <c r="G54" s="1">
-        <v>46207</v>
-      </c>
-      <c r="H54" s="43">
+        <v>46201</v>
+      </c>
+      <c r="H54" s="42">
         <v>0</v>
       </c>
       <c r="I54">
-        <v>-39</v>
+        <v>-41</v>
       </c>
       <c r="J54" t="s">
         <v>2284</v>
@@ -11596,13 +11599,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="B55" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" t="s">
         <v>186</v>
@@ -11614,13 +11617,13 @@
         <v>46200</v>
       </c>
       <c r="G55" s="1">
-        <v>46201</v>
-      </c>
-      <c r="H55" s="43">
+        <v>46203</v>
+      </c>
+      <c r="H55" s="42">
         <v>0</v>
       </c>
       <c r="I55">
-        <v>-41</v>
+        <v>-36</v>
       </c>
       <c r="J55" t="s">
         <v>2284</v>
@@ -11628,31 +11631,31 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>703</v>
+        <v>211</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>196</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D56" t="s">
         <v>186</v>
       </c>
       <c r="E56" t="s">
-        <v>681</v>
+        <v>35</v>
       </c>
       <c r="F56" s="1">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="G56" s="1">
-        <v>46203</v>
-      </c>
-      <c r="H56" s="43">
+        <v>46207</v>
+      </c>
+      <c r="H56" s="42">
         <v>0</v>
       </c>
       <c r="I56">
-        <v>-36</v>
+        <v>-25</v>
       </c>
       <c r="J56" t="s">
         <v>2284</v>
@@ -11660,31 +11663,31 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>211</v>
+        <v>1246</v>
       </c>
       <c r="B57" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D57" t="s">
         <v>186</v>
       </c>
       <c r="E57" t="s">
-        <v>35</v>
+        <v>1139</v>
       </c>
       <c r="F57" s="1">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="G57" s="1">
-        <v>46207</v>
-      </c>
-      <c r="H57" s="43">
+        <v>46209</v>
+      </c>
+      <c r="H57" s="42">
         <v>0</v>
       </c>
       <c r="I57">
-        <v>-25</v>
+        <v>-38</v>
       </c>
       <c r="J57" t="s">
         <v>2284</v>
@@ -11692,7 +11695,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="B58" t="s">
         <v>192</v>
@@ -11712,11 +11715,11 @@
       <c r="G58" s="1">
         <v>46209</v>
       </c>
-      <c r="H58" s="43">
+      <c r="H58" s="42">
         <v>0</v>
       </c>
       <c r="I58">
-        <v>-38</v>
+        <v>-27</v>
       </c>
       <c r="J58" t="s">
         <v>2284</v>
@@ -11724,31 +11727,31 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1252</v>
+        <v>212</v>
       </c>
       <c r="B59" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D59" t="s">
         <v>186</v>
       </c>
       <c r="E59" t="s">
-        <v>1139</v>
+        <v>35</v>
       </c>
       <c r="F59" s="1">
         <v>46202</v>
       </c>
       <c r="G59" s="1">
-        <v>46209</v>
-      </c>
-      <c r="H59" s="43">
+        <v>46208</v>
+      </c>
+      <c r="H59" s="42">
         <v>0</v>
       </c>
       <c r="I59">
-        <v>-27</v>
+        <v>-22</v>
       </c>
       <c r="J59" t="s">
         <v>2284</v>
@@ -11756,31 +11759,31 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>212</v>
+        <v>1247</v>
       </c>
       <c r="B60" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C60">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D60" t="s">
         <v>186</v>
       </c>
       <c r="E60" t="s">
-        <v>35</v>
+        <v>1139</v>
       </c>
       <c r="F60" s="1">
         <v>46202</v>
       </c>
       <c r="G60" s="1">
-        <v>46208</v>
-      </c>
-      <c r="H60" s="43">
+        <v>46209</v>
+      </c>
+      <c r="H60" s="42">
         <v>0</v>
       </c>
       <c r="I60">
-        <v>-22</v>
+        <v>-38</v>
       </c>
       <c r="J60" t="s">
         <v>2284</v>
@@ -11788,7 +11791,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="B61" t="s">
         <v>194</v>
@@ -11808,11 +11811,11 @@
       <c r="G61" s="1">
         <v>46209</v>
       </c>
-      <c r="H61" s="43">
+      <c r="H61" s="42">
         <v>0</v>
       </c>
       <c r="I61">
-        <v>-38</v>
+        <v>-27</v>
       </c>
       <c r="J61" t="s">
         <v>2284</v>
@@ -11820,31 +11823,31 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1253</v>
+        <v>694</v>
       </c>
       <c r="B62" t="s">
-        <v>194</v>
+        <v>73</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D62" t="s">
         <v>186</v>
       </c>
       <c r="E62" t="s">
-        <v>1139</v>
+        <v>681</v>
       </c>
       <c r="F62" s="1">
         <v>46202</v>
       </c>
       <c r="G62" s="1">
-        <v>46209</v>
-      </c>
-      <c r="H62" s="43">
+        <v>46205</v>
+      </c>
+      <c r="H62" s="42">
         <v>0</v>
       </c>
       <c r="I62">
-        <v>-27</v>
+        <v>-41</v>
       </c>
       <c r="J62" t="s">
         <v>2284</v>
@@ -11852,31 +11855,31 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>694</v>
+        <v>188</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D63" t="s">
         <v>186</v>
       </c>
       <c r="E63" t="s">
-        <v>681</v>
+        <v>35</v>
       </c>
       <c r="F63" s="1">
         <v>46202</v>
       </c>
       <c r="G63" s="1">
-        <v>46205</v>
-      </c>
-      <c r="H63" s="43">
+        <v>46210</v>
+      </c>
+      <c r="H63" s="42">
         <v>0</v>
       </c>
       <c r="I63">
-        <v>-41</v>
+        <v>-43</v>
       </c>
       <c r="J63" t="s">
         <v>2284</v>
@@ -11884,31 +11887,31 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>188</v>
+        <v>714</v>
       </c>
       <c r="B64" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D64" t="s">
         <v>186</v>
       </c>
       <c r="E64" t="s">
-        <v>35</v>
+        <v>681</v>
       </c>
       <c r="F64" s="1">
         <v>46202</v>
       </c>
       <c r="G64" s="1">
-        <v>46210</v>
-      </c>
-      <c r="H64" s="43">
+        <v>46205</v>
+      </c>
+      <c r="H64" s="42">
         <v>0</v>
       </c>
       <c r="I64">
-        <v>-43</v>
+        <v>-36</v>
       </c>
       <c r="J64" t="s">
         <v>2284</v>
@@ -11916,13 +11919,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D65" t="s">
         <v>186</v>
@@ -11934,13 +11937,13 @@
         <v>46202</v>
       </c>
       <c r="G65" s="1">
-        <v>46205</v>
-      </c>
-      <c r="H65" s="43">
+        <v>46208</v>
+      </c>
+      <c r="H65" s="42">
         <v>0</v>
       </c>
       <c r="I65">
-        <v>-36</v>
+        <v>-31</v>
       </c>
       <c r="J65" t="s">
         <v>2284</v>
@@ -11948,31 +11951,31 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>725</v>
+        <v>205</v>
       </c>
       <c r="B66" t="s">
-        <v>54</v>
+        <v>196</v>
       </c>
       <c r="C66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D66" t="s">
         <v>186</v>
       </c>
       <c r="E66" t="s">
-        <v>681</v>
+        <v>35</v>
       </c>
       <c r="F66" s="1">
         <v>46202</v>
       </c>
       <c r="G66" s="1">
-        <v>46208</v>
-      </c>
-      <c r="H66" s="43">
+        <v>46209</v>
+      </c>
+      <c r="H66" s="42">
         <v>0</v>
       </c>
       <c r="I66">
-        <v>-31</v>
+        <v>-39</v>
       </c>
       <c r="J66" t="s">
         <v>2284</v>
@@ -11980,10 +11983,10 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B67" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C67">
         <v>6</v>
@@ -12000,11 +12003,11 @@
       <c r="G67" s="1">
         <v>46209</v>
       </c>
-      <c r="H67" s="43">
+      <c r="H67" s="42">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>-39</v>
+        <v>-35</v>
       </c>
       <c r="J67" t="s">
         <v>2284</v>
@@ -12012,31 +12015,31 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>206</v>
+        <v>1705</v>
       </c>
       <c r="B68" t="s">
-        <v>198</v>
+        <v>58</v>
       </c>
       <c r="C68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D68" t="s">
         <v>186</v>
       </c>
       <c r="E68" t="s">
-        <v>35</v>
+        <v>1690</v>
       </c>
       <c r="F68" s="1">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="G68" s="1">
-        <v>46209</v>
-      </c>
-      <c r="H68" s="43">
+        <v>46207</v>
+      </c>
+      <c r="H68" s="42">
         <v>0</v>
       </c>
       <c r="I68">
-        <v>-35</v>
+        <v>-22</v>
       </c>
       <c r="J68" t="s">
         <v>2284</v>
@@ -12044,31 +12047,31 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1705</v>
+        <v>1969</v>
       </c>
       <c r="B69" t="s">
         <v>58</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D69" t="s">
         <v>186</v>
       </c>
       <c r="E69" t="s">
-        <v>1690</v>
+        <v>1941</v>
       </c>
       <c r="F69" s="1">
         <v>46203</v>
       </c>
       <c r="G69" s="1">
-        <v>46207</v>
-      </c>
-      <c r="H69" s="43">
+        <v>46205</v>
+      </c>
+      <c r="H69" s="42">
         <v>0</v>
       </c>
       <c r="I69">
-        <v>-22</v>
+        <v>-50</v>
       </c>
       <c r="J69" t="s">
         <v>2284</v>
@@ -12076,31 +12079,31 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1969</v>
+        <v>1715</v>
       </c>
       <c r="B70" t="s">
-        <v>58</v>
+        <v>1704</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D70" t="s">
         <v>186</v>
       </c>
       <c r="E70" t="s">
-        <v>1941</v>
+        <v>1690</v>
       </c>
       <c r="F70" s="1">
         <v>46203</v>
       </c>
       <c r="G70" s="1">
-        <v>46205</v>
-      </c>
-      <c r="H70" s="43">
+        <v>46214</v>
+      </c>
+      <c r="H70" s="42">
         <v>0</v>
       </c>
       <c r="I70">
-        <v>-50</v>
+        <v>-22</v>
       </c>
       <c r="J70" t="s">
         <v>2284</v>
@@ -12108,31 +12111,31 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1715</v>
+        <v>189</v>
       </c>
       <c r="B71" t="s">
-        <v>1704</v>
+        <v>92</v>
       </c>
       <c r="C71">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D71" t="s">
         <v>186</v>
       </c>
       <c r="E71" t="s">
-        <v>1690</v>
+        <v>35</v>
       </c>
       <c r="F71" s="1">
         <v>46203</v>
       </c>
       <c r="G71" s="1">
-        <v>46214</v>
-      </c>
-      <c r="H71" s="43">
+        <v>46210</v>
+      </c>
+      <c r="H71" s="42">
         <v>0</v>
       </c>
       <c r="I71">
-        <v>-22</v>
+        <v>-43</v>
       </c>
       <c r="J71" t="s">
         <v>2284</v>
@@ -12140,31 +12143,31 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>189</v>
+        <v>705</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="C72">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
       </c>
       <c r="E72" t="s">
-        <v>35</v>
+        <v>681</v>
       </c>
       <c r="F72" s="1">
         <v>46203</v>
       </c>
       <c r="G72" s="1">
-        <v>46210</v>
-      </c>
-      <c r="H72" s="43">
+        <v>46205</v>
+      </c>
+      <c r="H72" s="42">
         <v>0</v>
       </c>
       <c r="I72">
-        <v>-43</v>
+        <v>-36</v>
       </c>
       <c r="J72" t="s">
         <v>2284</v>
@@ -12172,10 +12175,10 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>705</v>
+        <v>1208</v>
       </c>
       <c r="B73" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C73">
         <v>2</v>
@@ -12184,33 +12187,33 @@
         <v>186</v>
       </c>
       <c r="E73" t="s">
-        <v>681</v>
+        <v>1139</v>
       </c>
       <c r="F73" s="1">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="G73" s="1">
         <v>46205</v>
       </c>
-      <c r="H73" s="43">
+      <c r="H73" s="42">
         <v>0</v>
       </c>
       <c r="I73">
-        <v>-36</v>
+        <v>8</v>
       </c>
       <c r="J73" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1208</v>
+        <v>1218</v>
       </c>
       <c r="B74" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D74" t="s">
         <v>186</v>
@@ -12222,47 +12225,15 @@
         <v>46204</v>
       </c>
       <c r="G74" s="1">
-        <v>46205</v>
-      </c>
-      <c r="H74" s="43">
+        <v>46215</v>
+      </c>
+      <c r="H74" s="42">
         <v>0</v>
       </c>
       <c r="I74">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="J74" t="s">
-        <v>2283</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>1218</v>
-      </c>
-      <c r="B75" t="s">
-        <v>54</v>
-      </c>
-      <c r="C75">
-        <v>10</v>
-      </c>
-      <c r="D75" t="s">
-        <v>186</v>
-      </c>
-      <c r="E75" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F75" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G75" s="1">
-        <v>46215</v>
-      </c>
-      <c r="H75" s="43">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>74</v>
-      </c>
-      <c r="J75" t="s">
         <v>2283</v>
       </c>
     </row>
@@ -12474,10 +12445,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="43" t="s">
         <v>2232</v>
       </c>
-      <c r="B1" s="42"/>
+      <c r="B1" s="43"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
@@ -12653,7 +12624,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12790,10 +12761,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E6">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThanOrEqual">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/project-dashboard.xlsx
+++ b/data/project-dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00-Maseel Project Control\11-Website Dashboard\Dynamic Web\project-dashboard-website\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A59438-D051-4A3B-B570-ED2F11B31368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC5804C-EFEC-444A-A220-8E88D00CBDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project_Info" sheetId="1" r:id="rId1"/>
@@ -7292,15 +7292,6 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -7431,6 +7422,30 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -7481,28 +7496,13 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9428,9 +9428,9 @@
     <tableColumn id="3" xr3:uid="{BEBE23B0-DD9A-46A0-83F0-F7AADFB113E0}" name="Original Duration"/>
     <tableColumn id="4" xr3:uid="{6FF22079-BD1C-473D-8452-4351A338CF7F}" name="Activity Status"/>
     <tableColumn id="5" xr3:uid="{07E5DDBB-1EE3-4BBE-A76E-96D7AC3BF882}" name="02- Con.Phase"/>
-    <tableColumn id="6" xr3:uid="{551887B7-0CF0-4401-9C1A-2DF3FF831FD4}" name="Start" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{947F443A-6D45-4251-B1BF-9CBC39B7A1B5}" name="Finish" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{62C03662-69E1-4727-A2DD-0879099C639A}" name="Performance % Complete" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{551887B7-0CF0-4401-9C1A-2DF3FF831FD4}" name="Start" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{947F443A-6D45-4251-B1BF-9CBC39B7A1B5}" name="Finish" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{62C03662-69E1-4727-A2DD-0879099C639A}" name="Performance % Complete" dataDxfId="43"/>
     <tableColumn id="9" xr3:uid="{5C1834A0-CE32-4342-8EF5-1EC543B01FAA}" name="Total Float"/>
     <tableColumn id="10" xr3:uid="{0293C0C3-272F-4BB3-B63E-9D3BC97471CF}" name="Critical"/>
   </tableColumns>
@@ -9460,13 +9460,13 @@
     <tableColumn id="4" xr3:uid="{26228A24-7B89-4F53-8C02-895BDE96807E}" name="Variance %">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{043BEE59-9BB9-48CA-BCAF-B0B49AB502E6}" name="SPI" dataDxfId="37">
+    <tableColumn id="5" xr3:uid="{043BEE59-9BB9-48CA-BCAF-B0B49AB502E6}" name="SPI" dataDxfId="42">
       <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{7FA7C1AA-84AA-4AEE-BAFB-D3FAEE25A5D8}" name="BL Start Date"/>
     <tableColumn id="7" xr3:uid="{4234B7FF-F64E-4A3A-9F37-5B5BEF6D9017}" name="BL Finish Date"/>
     <tableColumn id="8" xr3:uid="{3B605CB7-AB94-4F24-892D-8D23051F549D}" name="Forecast Finish Date"/>
-    <tableColumn id="9" xr3:uid="{8627A771-209F-4934-998C-3A0C21C0CC0E}" name="Variance Finish Date" dataDxfId="36">
+    <tableColumn id="9" xr3:uid="{8627A771-209F-4934-998C-3A0C21C0CC0E}" name="Variance Finish Date" dataDxfId="41">
       <calculatedColumnFormula>G2-H2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{E446F1CD-F15A-4A57-924F-E08331EF6928}" name="Project Duration"/>
@@ -9476,7 +9476,7 @@
     <tableColumn id="12" xr3:uid="{C8177739-B2D6-445C-909A-3B630381521D}" name="Remaining Time">
       <calculatedColumnFormula>J2-K2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{2413F253-FC61-4728-AA12-82814EB1AC1E}" name="Time Elapsed %" dataDxfId="35">
+    <tableColumn id="13" xr3:uid="{2413F253-FC61-4728-AA12-82814EB1AC1E}" name="Time Elapsed %" dataDxfId="40">
       <calculatedColumnFormula>K2/J2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9490,10 +9490,10 @@
     <tableColumn id="1" xr3:uid="{5CC08CFD-BB32-42AE-8929-3D92342465CF}" name="Phase"/>
     <tableColumn id="2" xr3:uid="{5D73634F-CCC4-411A-8B1A-98488EA6FA8F}" name="Planned %"/>
     <tableColumn id="3" xr3:uid="{32C402C6-661D-4391-B7B2-C3C85BB5AF80}" name="Actual %"/>
-    <tableColumn id="4" xr3:uid="{089AD09E-CE81-45D7-9664-49ACA4EE345D}" name="Variance" dataDxfId="34">
+    <tableColumn id="4" xr3:uid="{089AD09E-CE81-45D7-9664-49ACA4EE345D}" name="Variance" dataDxfId="39">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FA9B9069-F615-43F7-AF56-68E6B97329D8}" name="SPI" dataDxfId="33">
+    <tableColumn id="5" xr3:uid="{FA9B9069-F615-43F7-AF56-68E6B97329D8}" name="SPI" dataDxfId="38">
       <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9509,46 +9509,46 @@
     <tableColumn id="3" xr3:uid="{EEFE8DE6-C657-48D9-88FA-7D5A43C1590A}" name="Original Duration"/>
     <tableColumn id="4" xr3:uid="{BFD618A5-3D3D-4C62-9AEE-667429FF6625}" name="Activity Status"/>
     <tableColumn id="5" xr3:uid="{54C85E9C-40B3-4A27-A7A1-08D5632ACFD5}" name="02- Con.Phase"/>
-    <tableColumn id="6" xr3:uid="{1E54E21F-3570-4379-98B5-D3F79BAD2A54}" name="BL Project Start" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{8AF72BC8-3D95-4695-BE78-28DE430A0C96}" name="BL Project Finish" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{41D5B848-CED1-4B85-B7C0-0C2EEADFA08F}" name="Start" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{6993DFB5-C059-4A89-9ABD-71F49C2A6F74}" name="Finish" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{9EAC2262-2A27-42A8-BB73-73F39AFC4912}" name="Schedule % Complete" dataDxfId="28" dataCellStyle="Per cent"/>
-    <tableColumn id="11" xr3:uid="{B218F782-EF65-4945-9E84-E0A88975643B}" name="Performance % Complete" dataDxfId="27" dataCellStyle="Per cent"/>
-    <tableColumn id="12" xr3:uid="{85C93BA9-907D-4549-9ECD-E1601A6B8FF1}" name="Total Float" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{C49B17F2-109E-42EB-814F-75ABCAF72ADF}" name="Critical" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{1E54E21F-3570-4379-98B5-D3F79BAD2A54}" name="BL Project Start" dataDxfId="37"/>
+    <tableColumn id="7" xr3:uid="{8AF72BC8-3D95-4695-BE78-28DE430A0C96}" name="BL Project Finish" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{41D5B848-CED1-4B85-B7C0-0C2EEADFA08F}" name="Start" dataDxfId="35"/>
+    <tableColumn id="9" xr3:uid="{6993DFB5-C059-4A89-9ABD-71F49C2A6F74}" name="Finish" dataDxfId="34"/>
+    <tableColumn id="10" xr3:uid="{9EAC2262-2A27-42A8-BB73-73F39AFC4912}" name="Schedule % Complete" dataDxfId="33" dataCellStyle="Per cent"/>
+    <tableColumn id="11" xr3:uid="{B218F782-EF65-4945-9E84-E0A88975643B}" name="Performance % Complete" dataDxfId="32" dataCellStyle="Per cent"/>
+    <tableColumn id="12" xr3:uid="{85C93BA9-907D-4549-9ECD-E1601A6B8FF1}" name="Total Float" dataDxfId="31"/>
+    <tableColumn id="13" xr3:uid="{C49B17F2-109E-42EB-814F-75ABCAF72ADF}" name="Critical" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{646BB870-B00C-435D-A3B9-FC5EE922B49E}" name="DelaysTable16" displayName="DelaysTable16" ref="A1:G7" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{646BB870-B00C-435D-A3B9-FC5EE922B49E}" name="DelaysTable16" displayName="DelaysTable16" ref="A1:G7" dataDxfId="29">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{432610E1-EB61-4ACD-97A4-8A63654F84F9}" name="Phase Delay/Ahead" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{2C5412A7-92CE-4EAC-8330-FA329E02B968}" name="BL Finish Date" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{0E5F2071-69D2-4243-B28B-C06740FB7648}" name="Forecast Finish Date" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{E02C79E2-295D-4560-9843-63A6C0451E21}" name="Variance Finish Date" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{5A1277A0-CB8F-43B1-BC65-D584276375E2}" name="Delay Reason" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{3E4DC573-6186-4CC7-8D6B-0A44D59D4182}" name="Recovery Action" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{C16296EE-BD20-4329-86E5-BA92EF668C0A}" name="Responsible" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{432610E1-EB61-4ACD-97A4-8A63654F84F9}" name="Phase Delay/Ahead" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{2C5412A7-92CE-4EAC-8330-FA329E02B968}" name="BL Finish Date" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{0E5F2071-69D2-4243-B28B-C06740FB7648}" name="Forecast Finish Date" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{E02C79E2-295D-4560-9843-63A6C0451E21}" name="Variance Finish Date" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{5A1277A0-CB8F-43B1-BC65-D584276375E2}" name="Delay Reason" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{3E4DC573-6186-4CC7-8D6B-0A44D59D4182}" name="Recovery Action" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{C16296EE-BD20-4329-86E5-BA92EF668C0A}" name="Responsible" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="IssuesRisksTable" displayName="IssuesRisksTable" ref="A1:I6" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="IssuesRisksTable" displayName="IssuesRisksTable" ref="A1:I6" dataDxfId="21">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Risk ID" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Risk Description" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Impact Summary" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Probability" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Impact" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Risk Level" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Risk Owner" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Mitigation" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="Target Date" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Risk ID" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Risk Description" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Impact Summary" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Probability" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Impact" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Risk Level" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Risk Owner" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Mitigation" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="Target Date" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9570,15 +9570,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{A2B8666E-147E-4183-82CC-79B74FF1D518}" name="SPITrendTable17" displayName="SPITrendTable17" ref="A1:J2">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{60CDD5EE-B607-4D51-A2AC-550AB14A03F3}" name="Month"/>
-    <tableColumn id="2" xr3:uid="{76772940-DA13-40AE-BA52-917177C89224}" name="01-Feb-2026" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{F0248E2B-506D-42FB-B594-3D1B0C0B4368}" name="01-Mar-2026" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{1235EC57-E169-4937-B53F-0C4A6D4C5E0F}" name="01-Apr-2026" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{7E0642A5-711D-421D-9854-5659F4096F36}" name="01-May-2026" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{88D79C57-C3FB-4564-A7BE-EDB347046130}" name="01-Jun-2026" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{FBD55C5C-8427-4396-A9A1-D8D5EEDAA0F8}" name="01-Jul-2026" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{16A53D90-2572-4B4A-B792-FF1B1888C5A4}" name="01-Aug-2026" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{153860B1-419C-48D2-8D33-F85625CFBC01}" name="01-Sep-2026" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{C6E67E4F-856C-4338-B620-93C903A271F9}" name="01-Oct-2026" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{76772940-DA13-40AE-BA52-917177C89224}" name="01-Feb-2026" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{F0248E2B-506D-42FB-B594-3D1B0C0B4368}" name="01-Mar-2026" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{1235EC57-E169-4937-B53F-0C4A6D4C5E0F}" name="01-Apr-2026" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{7E0642A5-711D-421D-9854-5659F4096F36}" name="01-May-2026" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{88D79C57-C3FB-4564-A7BE-EDB347046130}" name="01-Jun-2026" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{FBD55C5C-8427-4396-A9A1-D8D5EEDAA0F8}" name="01-Jul-2026" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{16A53D90-2572-4B4A-B792-FF1B1888C5A4}" name="01-Aug-2026" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{153860B1-419C-48D2-8D33-F85625CFBC01}" name="01-Sep-2026" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{C6E67E4F-856C-4338-B620-93C903A271F9}" name="01-Oct-2026" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -91291,7 +91291,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>26</v>
@@ -91305,7 +91305,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>27</v>
@@ -91319,7 +91319,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>28</v>
@@ -91333,7 +91333,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>29</v>
@@ -91347,7 +91347,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>30</v>

--- a/data/project-dashboard.xlsx
+++ b/data/project-dashboard.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B9E9BD-59E0-4915-A1F6-289588DEF23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project_Info" sheetId="1" r:id="rId1"/>

--- a/data/project-dashboard.xlsx
+++ b/data/project-dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00-Maseel Project Control\11-Website Dashboard\Dynamic Web\project-dashboard-website\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4786D23B-8DD4-4C61-BEEA-17A79EFE9B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965299B6-D534-454F-8DC4-2EFC25B7072E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="855" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project_Info" sheetId="1" r:id="rId1"/>
@@ -7035,7 +7035,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="168" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -7306,11 +7306,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="169" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -7349,15 +7349,6 @@
           <bgColor rgb="FFF8CBAD"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
@@ -7575,6 +7566,15 @@
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8169,7 +8169,7 @@
                   <c:v>1.6554800333872452E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.4196214867476062E-2</c:v>
+                  <c:v>1.962548398355797E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8588,7 +8588,7 @@
                   <c:v>8.8454800333872458E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.10265101520134852</c:v>
+                  <c:v>0.109651015201349</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9506,9 +9506,9 @@
     <tableColumn id="3" xr3:uid="{BEBE23B0-DD9A-46A0-83F0-F7AADFB113E0}" name="Original Duration"/>
     <tableColumn id="4" xr3:uid="{6FF22079-BD1C-473D-8452-4351A338CF7F}" name="Activity Status"/>
     <tableColumn id="5" xr3:uid="{07E5DDBB-1EE3-4BBE-A76E-96D7AC3BF882}" name="02- Con.Phase"/>
-    <tableColumn id="6" xr3:uid="{551887B7-0CF0-4401-9C1A-2DF3FF831FD4}" name="Start" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{947F443A-6D45-4251-B1BF-9CBC39B7A1B5}" name="Finish" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{62C03662-69E1-4727-A2DD-0879099C639A}" name="Performance % Complete" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{551887B7-0CF0-4401-9C1A-2DF3FF831FD4}" name="Start" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{947F443A-6D45-4251-B1BF-9CBC39B7A1B5}" name="Finish" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{62C03662-69E1-4727-A2DD-0879099C639A}" name="Performance % Complete" dataDxfId="44"/>
     <tableColumn id="9" xr3:uid="{5C1834A0-CE32-4342-8EF5-1EC543B01FAA}" name="Total Float"/>
     <tableColumn id="10" xr3:uid="{0293C0C3-272F-4BB3-B63E-9D3BC97471CF}" name="Critical"/>
   </tableColumns>
@@ -9532,19 +9532,19 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{81FF45E3-C5EB-471F-ABB4-28B38626C1F3}" name="OverallProgressTable" displayName="OverallProgressTable" ref="A1:M2">
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{F857827D-16AE-48BF-880E-D8DA9F135CBC}" name="Report Date" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{F857827D-16AE-48BF-880E-D8DA9F135CBC}" name="Report Date" dataDxfId="43"/>
     <tableColumn id="2" xr3:uid="{B8C1FD56-D96E-4AAA-A29F-46890EDE51D3}" name="Planned %"/>
     <tableColumn id="3" xr3:uid="{CC73173A-3871-4BD5-9FE6-C16CAA3EAD66}" name="Actual %"/>
     <tableColumn id="4" xr3:uid="{26228A24-7B89-4F53-8C02-895BDE96807E}" name="Variance %">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{043BEE59-9BB9-48CA-BCAF-B0B49AB502E6}" name="SPI" dataDxfId="45">
+    <tableColumn id="5" xr3:uid="{043BEE59-9BB9-48CA-BCAF-B0B49AB502E6}" name="SPI" dataDxfId="42">
       <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{7FA7C1AA-84AA-4AEE-BAFB-D3FAEE25A5D8}" name="BL Start Date"/>
     <tableColumn id="7" xr3:uid="{4234B7FF-F64E-4A3A-9F37-5B5BEF6D9017}" name="BL Finish Date"/>
     <tableColumn id="8" xr3:uid="{3B605CB7-AB94-4F24-892D-8D23051F549D}" name="Forecast Finish Date"/>
-    <tableColumn id="9" xr3:uid="{8627A771-209F-4934-998C-3A0C21C0CC0E}" name="Variance Finish Date" dataDxfId="44">
+    <tableColumn id="9" xr3:uid="{8627A771-209F-4934-998C-3A0C21C0CC0E}" name="Variance Finish Date" dataDxfId="41">
       <calculatedColumnFormula>G2-H2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{E446F1CD-F15A-4A57-924F-E08331EF6928}" name="Project Duration"/>
@@ -9554,7 +9554,7 @@
     <tableColumn id="12" xr3:uid="{C8177739-B2D6-445C-909A-3B630381521D}" name="Remaining Time">
       <calculatedColumnFormula>J2-K2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{2413F253-FC61-4728-AA12-82814EB1AC1E}" name="Time Elapsed %" dataDxfId="43">
+    <tableColumn id="13" xr3:uid="{2413F253-FC61-4728-AA12-82814EB1AC1E}" name="Time Elapsed %" dataDxfId="40">
       <calculatedColumnFormula>K2/J2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9568,10 +9568,10 @@
     <tableColumn id="1" xr3:uid="{5CC08CFD-BB32-42AE-8929-3D92342465CF}" name="Phase"/>
     <tableColumn id="2" xr3:uid="{5D73634F-CCC4-411A-8B1A-98488EA6FA8F}" name="Planned %"/>
     <tableColumn id="3" xr3:uid="{32C402C6-661D-4391-B7B2-C3C85BB5AF80}" name="Actual %"/>
-    <tableColumn id="4" xr3:uid="{089AD09E-CE81-45D7-9664-49ACA4EE345D}" name="Variance" dataDxfId="42">
+    <tableColumn id="4" xr3:uid="{089AD09E-CE81-45D7-9664-49ACA4EE345D}" name="Variance" dataDxfId="39">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FA9B9069-F615-43F7-AF56-68E6B97329D8}" name="SPI" dataDxfId="41">
+    <tableColumn id="5" xr3:uid="{FA9B9069-F615-43F7-AF56-68E6B97329D8}" name="SPI" dataDxfId="38">
       <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9587,46 +9587,46 @@
     <tableColumn id="3" xr3:uid="{EEFE8DE6-C657-48D9-88FA-7D5A43C1590A}" name="Original Duration"/>
     <tableColumn id="4" xr3:uid="{BFD618A5-3D3D-4C62-9AEE-667429FF6625}" name="Activity Status"/>
     <tableColumn id="5" xr3:uid="{54C85E9C-40B3-4A27-A7A1-08D5632ACFD5}" name="02- Con.Phase"/>
-    <tableColumn id="6" xr3:uid="{1E54E21F-3570-4379-98B5-D3F79BAD2A54}" name="BL Project Start" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{8AF72BC8-3D95-4695-BE78-28DE430A0C96}" name="BL Project Finish" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{41D5B848-CED1-4B85-B7C0-0C2EEADFA08F}" name="Start" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{6993DFB5-C059-4A89-9ABD-71F49C2A6F74}" name="Finish" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{9EAC2262-2A27-42A8-BB73-73F39AFC4912}" name="Schedule % Complete" dataDxfId="36" dataCellStyle="Per cent"/>
-    <tableColumn id="11" xr3:uid="{B218F782-EF65-4945-9E84-E0A88975643B}" name="Performance % Complete" dataDxfId="35" dataCellStyle="Per cent"/>
-    <tableColumn id="12" xr3:uid="{85C93BA9-907D-4549-9ECD-E1601A6B8FF1}" name="Total Float" dataDxfId="34"/>
-    <tableColumn id="13" xr3:uid="{C49B17F2-109E-42EB-814F-75ABCAF72ADF}" name="Critical" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{1E54E21F-3570-4379-98B5-D3F79BAD2A54}" name="BL Project Start" dataDxfId="37"/>
+    <tableColumn id="7" xr3:uid="{8AF72BC8-3D95-4695-BE78-28DE430A0C96}" name="BL Project Finish" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{41D5B848-CED1-4B85-B7C0-0C2EEADFA08F}" name="Start" dataDxfId="35"/>
+    <tableColumn id="9" xr3:uid="{6993DFB5-C059-4A89-9ABD-71F49C2A6F74}" name="Finish" dataDxfId="34"/>
+    <tableColumn id="10" xr3:uid="{9EAC2262-2A27-42A8-BB73-73F39AFC4912}" name="Schedule % Complete" dataDxfId="33" dataCellStyle="Per cent"/>
+    <tableColumn id="11" xr3:uid="{B218F782-EF65-4945-9E84-E0A88975643B}" name="Performance % Complete" dataDxfId="32" dataCellStyle="Per cent"/>
+    <tableColumn id="12" xr3:uid="{85C93BA9-907D-4549-9ECD-E1601A6B8FF1}" name="Total Float" dataDxfId="31"/>
+    <tableColumn id="13" xr3:uid="{C49B17F2-109E-42EB-814F-75ABCAF72ADF}" name="Critical" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{646BB870-B00C-435D-A3B9-FC5EE922B49E}" name="DelaysTable16" displayName="DelaysTable16" ref="A1:G9" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{646BB870-B00C-435D-A3B9-FC5EE922B49E}" name="DelaysTable16" displayName="DelaysTable16" ref="A1:G9" dataDxfId="29">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{432610E1-EB61-4ACD-97A4-8A63654F84F9}" name="Phase Delay/Ahead" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{2C5412A7-92CE-4EAC-8330-FA329E02B968}" name="BL Finish Date" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{0E5F2071-69D2-4243-B28B-C06740FB7648}" name="Forecast Finish Date" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{E02C79E2-295D-4560-9843-63A6C0451E21}" name="Variance Finish Date" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{5A1277A0-CB8F-43B1-BC65-D584276375E2}" name="Delay Reason" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{3E4DC573-6186-4CC7-8D6B-0A44D59D4182}" name="Recovery Action" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{C16296EE-BD20-4329-86E5-BA92EF668C0A}" name="Responsible" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{432610E1-EB61-4ACD-97A4-8A63654F84F9}" name="Phase Delay/Ahead" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{2C5412A7-92CE-4EAC-8330-FA329E02B968}" name="BL Finish Date" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{0E5F2071-69D2-4243-B28B-C06740FB7648}" name="Forecast Finish Date" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{E02C79E2-295D-4560-9843-63A6C0451E21}" name="Variance Finish Date" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{5A1277A0-CB8F-43B1-BC65-D584276375E2}" name="Delay Reason" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{3E4DC573-6186-4CC7-8D6B-0A44D59D4182}" name="Recovery Action" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{C16296EE-BD20-4329-86E5-BA92EF668C0A}" name="Responsible" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="IssuesRisksTable" displayName="IssuesRisksTable" ref="A1:I6" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="IssuesRisksTable" displayName="IssuesRisksTable" ref="A1:I6" dataDxfId="21">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Risk ID" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Risk Description" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Impact Summary" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Probability" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Impact" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Risk Level" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Risk Owner" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Mitigation" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="Target Date" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Risk ID" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Risk Description" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Impact Summary" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Probability" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Impact" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Risk Level" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Risk Owner" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Mitigation" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="Target Date" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9648,15 +9648,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{A2B8666E-147E-4183-82CC-79B74FF1D518}" name="SPITrendTable17" displayName="SPITrendTable17" ref="A1:J2">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{60CDD5EE-B607-4D51-A2AC-550AB14A03F3}" name="Month"/>
-    <tableColumn id="2" xr3:uid="{76772940-DA13-40AE-BA52-917177C89224}" name="01-Feb-2026" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{F0248E2B-506D-42FB-B594-3D1B0C0B4368}" name="01-Mar-2026" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{1235EC57-E169-4937-B53F-0C4A6D4C5E0F}" name="01-Apr-2026" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{7E0642A5-711D-421D-9854-5659F4096F36}" name="01-May-2026" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{88D79C57-C3FB-4564-A7BE-EDB347046130}" name="01-Jun-2026" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{FBD55C5C-8427-4396-A9A1-D8D5EEDAA0F8}" name="01-Jul-2026" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{16A53D90-2572-4B4A-B792-FF1B1888C5A4}" name="01-Aug-2026" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{153860B1-419C-48D2-8D33-F85625CFBC01}" name="01-Sep-2026" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{C6E67E4F-856C-4338-B620-93C903A271F9}" name="01-Oct-2026" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{76772940-DA13-40AE-BA52-917177C89224}" name="01-Feb-2026" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{F0248E2B-506D-42FB-B594-3D1B0C0B4368}" name="01-Mar-2026" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{1235EC57-E169-4937-B53F-0C4A6D4C5E0F}" name="01-Apr-2026" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{7E0642A5-711D-421D-9854-5659F4096F36}" name="01-May-2026" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{88D79C57-C3FB-4564-A7BE-EDB347046130}" name="01-Jun-2026" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{FBD55C5C-8427-4396-A9A1-D8D5EEDAA0F8}" name="01-Jul-2026" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{16A53D90-2572-4B4A-B792-FF1B1888C5A4}" name="01-Aug-2026" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{153860B1-419C-48D2-8D33-F85625CFBC01}" name="01-Sep-2026" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{C6E67E4F-856C-4338-B620-93C903A271F9}" name="01-Oct-2026" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12575,10 +12575,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>416</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="46"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
@@ -12802,15 +12802,15 @@
         <v>0.15122453334672306</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1486135345141408</v>
+        <v>0.151</v>
       </c>
       <c r="D2" s="14">
         <f>C2-B2</f>
-        <v>-2.6109988325822564E-3</v>
-      </c>
-      <c r="E2" s="46">
+        <v>-2.2453334672306591E-4</v>
+      </c>
+      <c r="E2" s="45">
         <f>C2/B2</f>
-        <v>0.9827342906947788</v>
+        <v>0.99851523200796877</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -12821,15 +12821,15 @@
         <v>2.0791392654229857E-2</v>
       </c>
       <c r="C3" s="14">
-        <v>2.0623629937815954E-2</v>
+        <v>2.0791392654229857E-2</v>
       </c>
       <c r="D3" s="14">
         <f t="shared" ref="D3:D6" si="0">C3-B3</f>
-        <v>-1.6776271641390228E-4</v>
-      </c>
-      <c r="E3" s="46">
+        <v>0</v>
+      </c>
+      <c r="E3" s="45">
         <f t="shared" ref="E3:E6" si="1">C3/B3</f>
-        <v>0.99193114577729968</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -12840,15 +12840,15 @@
         <v>0.10492911048659573</v>
       </c>
       <c r="C4" s="14">
-        <v>0.10432915469386467</v>
+        <v>0.10492911048659573</v>
       </c>
       <c r="D4" s="14">
         <f t="shared" si="0"/>
-        <v>-5.9995579273106059E-4</v>
-      </c>
-      <c r="E4" s="46">
+        <v>0</v>
+      </c>
+      <c r="E4" s="45">
         <f t="shared" si="1"/>
-        <v>0.99428227505266331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -12859,15 +12859,15 @@
         <v>7.1802325581395345E-3</v>
       </c>
       <c r="C5" s="14">
-        <v>7.1511627906976748E-3</v>
+        <v>7.1802325581395345E-3</v>
       </c>
       <c r="D5" s="14">
         <f t="shared" si="0"/>
-        <v>-2.9069767441859684E-5</v>
-      </c>
-      <c r="E5" s="46">
+        <v>0</v>
+      </c>
+      <c r="E5" s="45">
         <f t="shared" si="1"/>
-        <v>0.99595141700404866</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -12884,7 +12884,7 @@
         <f t="shared" si="0"/>
         <v>8.9606668403230047E-3</v>
       </c>
-      <c r="E6" s="46">
+      <c r="E6" s="45">
         <f t="shared" si="1"/>
         <v>1.1452089489235966</v>
       </c>
@@ -12961,7 +12961,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>506</v>
       </c>
@@ -13386,7 +13386,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>517</v>
       </c>
@@ -13620,7 +13620,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>523</v>
       </c>
@@ -14400,7 +14400,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
         <v>543</v>
       </c>
@@ -14556,7 +14556,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="16" t="s">
         <v>547</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
         <v>548</v>
       </c>
@@ -15020,7 +15020,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
         <v>559</v>
       </c>
@@ -15490,7 +15490,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="16" t="s">
         <v>570</v>
       </c>
@@ -15568,7 +15568,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="16" t="s">
         <v>572</v>
       </c>
@@ -15646,7 +15646,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="16" t="s">
         <v>574</v>
       </c>
@@ -15685,7 +15685,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="16" t="s">
         <v>575</v>
       </c>
@@ -15919,7 +15919,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="16" t="s">
         <v>581</v>
       </c>
@@ -15958,7 +15958,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="16" t="s">
         <v>582</v>
       </c>
@@ -16075,7 +16075,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="16" t="s">
         <v>585</v>
       </c>
@@ -16231,7 +16231,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A86" s="16" t="s">
         <v>589</v>
       </c>
@@ -16621,7 +16621,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="16" t="s">
         <v>599</v>
       </c>
@@ -16660,7 +16660,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A97" s="16" t="s">
         <v>600</v>
       </c>
@@ -16939,7 +16939,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="16" t="s">
         <v>127</v>
       </c>
@@ -16980,7 +16980,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A105" s="16" t="s">
         <v>604</v>
       </c>
@@ -17097,7 +17097,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="16" t="s">
         <v>607</v>
       </c>
@@ -17136,7 +17136,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A109" s="16" t="s">
         <v>608</v>
       </c>
@@ -17374,7 +17374,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="16" t="s">
         <v>305</v>
       </c>
@@ -17454,7 +17454,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="16" t="s">
         <v>283</v>
       </c>
@@ -18252,7 +18252,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A137" s="16" t="s">
         <v>309</v>
       </c>
@@ -18904,7 +18904,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A153" s="16" t="s">
         <v>296</v>
       </c>
@@ -19109,7 +19109,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A158" s="16" t="s">
         <v>132</v>
       </c>
@@ -20048,7 +20048,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A181" s="16" t="s">
         <v>199</v>
       </c>
@@ -20171,7 +20171,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A184" s="16" t="s">
         <v>246</v>
       </c>
@@ -21399,7 +21399,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A214" s="16" t="s">
         <v>631</v>
       </c>
@@ -22137,7 +22137,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A232" s="16" t="s">
         <v>645</v>
       </c>
@@ -23285,7 +23285,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A260" s="16" t="s">
         <v>673</v>
       </c>
@@ -23449,7 +23449,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A264" s="16" t="s">
         <v>677</v>
       </c>
@@ -23818,7 +23818,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A273" s="16" t="s">
         <v>686</v>
       </c>
@@ -23941,7 +23941,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A276" s="16" t="s">
         <v>689</v>
       </c>
@@ -24023,7 +24023,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A278" s="16" t="s">
         <v>691</v>
       </c>
@@ -24146,7 +24146,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A281" s="16" t="s">
         <v>694</v>
       </c>
@@ -25417,7 +25417,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A312" s="16" t="s">
         <v>725</v>
       </c>
@@ -25909,7 +25909,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A324" s="16" t="s">
         <v>737</v>
       </c>
@@ -28287,7 +28287,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A382" s="16" t="s">
         <v>795</v>
       </c>
@@ -28369,7 +28369,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A384" s="16" t="s">
         <v>288</v>
       </c>
@@ -29927,7 +29927,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A422" s="16" t="s">
         <v>834</v>
       </c>
@@ -33494,7 +33494,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A509" s="16" t="s">
         <v>921</v>
       </c>
@@ -37266,7 +37266,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A601" s="16" t="s">
         <v>1013</v>
       </c>
@@ -52764,7 +52764,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="979" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="979" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A979" s="16" t="s">
         <v>1391</v>
       </c>
@@ -55839,7 +55839,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="1054" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1054" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1054" s="16" t="s">
         <v>1466</v>
       </c>
@@ -58053,7 +58053,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="1108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1108" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1108" s="16" t="s">
         <v>1520</v>
       </c>
@@ -60062,7 +60062,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="1157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1157" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1157" s="16" t="s">
         <v>1569</v>
       </c>
@@ -61210,7 +61210,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="1185" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1185" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1185" s="16" t="s">
         <v>1597</v>
       </c>
@@ -61333,7 +61333,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="1188" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1188" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1188" s="16" t="s">
         <v>1600</v>
       </c>
@@ -64490,7 +64490,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="1265" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1265" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1265" s="16" t="s">
         <v>1677</v>
       </c>
@@ -65310,7 +65310,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="1285" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1285" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1285" s="16" t="s">
         <v>1697</v>
       </c>
@@ -66499,7 +66499,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="1314" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1314" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1314" s="16" t="s">
         <v>1726</v>
       </c>
@@ -70271,7 +70271,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1406" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1406" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1406" s="16" t="s">
         <v>1818</v>
       </c>
@@ -70681,7 +70681,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1416" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1416" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1416" s="16" t="s">
         <v>1828</v>
       </c>
@@ -70886,7 +70886,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="1421" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1421" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1421" s="16" t="s">
         <v>1833</v>
       </c>
@@ -72362,7 +72362,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="1457" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1457" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1457" s="16" t="s">
         <v>1869</v>
       </c>
@@ -74658,7 +74658,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1513" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1513" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1513" s="16" t="s">
         <v>1925</v>
       </c>
@@ -75314,7 +75314,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1529" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1529" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1529" s="16" t="s">
         <v>1941</v>
       </c>
@@ -76503,7 +76503,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="1558" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1558" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1558" s="16" t="s">
         <v>1970</v>
       </c>
@@ -80111,7 +80111,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="1646" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1646" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1646" s="16" t="s">
         <v>2058</v>
       </c>
@@ -86261,7 +86261,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="1796" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1796" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1796" s="16" t="s">
         <v>2208</v>
       </c>
@@ -91791,7 +91791,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
@@ -92021,7 +92021,7 @@
         <v>1.6554800333872452E-2</v>
       </c>
       <c r="J4" s="24">
-        <v>1.4196214867476062E-2</v>
+        <v>1.962548398355797E-2</v>
       </c>
       <c r="K4" s="24"/>
       <c r="L4" s="24"/>
@@ -92062,7 +92062,7 @@
         <v>8.8454800333872458E-2</v>
       </c>
       <c r="J5" s="24">
-        <v>0.10265101520134852</v>
+        <v>0.109651015201349</v>
       </c>
       <c r="K5" s="24"/>
       <c r="L5" s="24"/>
@@ -92074,6 +92074,10 @@
       <c r="R5" s="24"/>
       <c r="S5" s="24"/>
     </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
